--- a/Veterinary_care_Diligence_File_Tables_Oct-26.xlsx
+++ b/Veterinary_care_Diligence_File_Tables_Oct-26.xlsx
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Alpha - FY27 Clinic Closure Data, Summary!J43, J33, B49; fees ABC Private Credit Deal A Model v24, MODEL OUTPUT!F21; note C-FIN-4</t>
+          <t>Alpha - FY27 Clinic Closure Data, Summary!J43, J33, B49; fees Alder Point Credit Deal A Model v24, MODEL OUTPUT!F21; note C-FIN-4</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Row 152 is the bank model's principal line; ABC Private Credit's model nets the interest out (MODEL OUTPUT!D30, D171)</t>
+          <t>Row 152 is the bank model's principal line; Alder Point Credit's model nets the interest out (MODEL OUTPUT!D30, D171)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model v24 as it stands: EBITDA, $12m closure benefit from April 2027, capex, working capital, taxes, $177.7m of supplier-finance payments</t>
+          <t>Alder Point Credit's model v24 as it stands: EBITDA, $12m closure benefit from April 2027, capex, working capital, taxes, $177.7m of supplier-finance payments</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit Deal A Model v24, MODEL OUTPUT rows 13 to 28</t>
+          <t>Alder Point Credit Deal A Model v24, MODEL OUTPUT rows 13 to 28</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>EBITDA 9% below ABC Private Credit's model in every period; no closure benefit</t>
+          <t>EBITDA 9% below Alder Point Credit's model in every period; no closure benefit</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>$13m is the minimum cash in ABC Private Credit's model (MODEL OUTPUT!F159:L159); note C-FIN-3</t>
+          <t>$13m is the minimum cash in Alder Point Credit's model (MODEL OUTPUT!F159:L159); note C-FIN-3</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>FY27 Closing Clinics Financial Analysis, Summary!J43; fees ABC Private Credit Deal A Model v24, MODEL OUTPUT!F21; note C-V2-4</t>
+          <t>FY27 Closing Clinics Financial Analysis, Summary!J43; fees Alder Point Credit Deal A Model v24, MODEL OUTPUT!F21; note C-V2-4</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit hypothesis or ABC Private Credit model output</t>
+          <t>Alder Point Credit hypothesis or Alder Point Credit model output</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.11 — Twelve forms of reference, each resolving in a named section of this document, in a document ABC Private Credit holds or at a public address with the date it was read</t>
+          <t>Exhibit 9.11 — Twelve forms of reference, each resolving in a named section of this document, in a document Alder Point Credit holds or at a public address with the date it was read</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>A document ABC Private Credit supplied, by source ID or short name, and the page</t>
+          <t>A document Alder Point Credit supplied, by source ID or short name, and the page</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>A workbook ABC Private Credit supplied, the tab and the cell or range</t>
+          <t>A workbook Alder Point Credit supplied, the tab and the cell or range</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Deal A (including the ABC Private Credit model)</t>
+          <t>Deal A (including the Alder Point Credit model)</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.14 — Each supplied document is cited by one ID that resolves to its file name as ABC Private Credit holds it and its date; Deal A's public filings are one entry</t>
+          <t>Exhibit 9.14 — Each supplied document is cited by one ID that resolves to its file name as Alder Point Credit holds it and its date; Deal A's public filings are one entry</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>File name as ABC Private Credit holds it</t>
+          <t>File name as Alder Point Credit holds it</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
@@ -4407,14 +4407,14 @@
     <row r="207" ht="30" customHeight="1">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.15 — Six source files received on 1 October 2026 were read: four on Deal A's financing, second round and current trading, and Deal B's and DBW's answers to ABC Private Credit's diligence questions</t>
+          <t>Exhibit 9.15 — Six source files received on 1 October 2026 were read: four on Deal A's financing, second round and current trading, and Deal B's and DBW's answers to Alder Point Credit's diligence questions</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="8" t="inlineStr">
         <is>
-          <t>Registry ID, short name, file name as ABC Private Credit holds it with its folder, document date, what the document is and the evidence tag its figures carry; the other 49 files received that day are copies of files already held</t>
+          <t>Registry ID, short name, file name as Alder Point Credit holds it with its folder, document date, what the document is and the evidence tag its figures carry; the other 49 files received that day are copies of files already held</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>File as ABC Private Credit holds it</t>
+          <t>File as Alder Point Credit holds it</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="B214" s="7" t="inlineStr">
         <is>
-          <t>DLB ABC Private Credit Diligence Responses</t>
+          <t>DLB Alder Point Credit Diligence Responses</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>NEW FILES OCT 1/Deal B/DLB ABC Private Credit Diligence [file]</t>
+          <t>NEW FILES OCT 1/Deal B/DLB Alder Point Credit Diligence [file]</t>
         </is>
       </c>
       <c r="D214" s="7" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>DBW ABC Private Credit Diligence Responses</t>
+          <t>DBW Alder Point Credit Diligence Responses</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>NEW FILES OCT 1/Deal B/DBW ABC Private Credit Diligence [file]</t>
+          <t>NEW FILES OCT 1/Deal B/DBW Alder Point Credit Diligence [file]</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
@@ -12660,7 +12660,7 @@
     <row r="463">
       <c r="A463" s="7" t="inlineStr">
         <is>
-          <t>Rows read from ABC Private Credit's investment memos (IDs P5-S)</t>
+          <t>Rows read from Alder Point Credit's investment memos (IDs P5-S)</t>
         </is>
       </c>
       <c r="B463" s="10" t="n">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="D522" s="7" t="inlineStr">
         <is>
-          <t>DLB-031 internal QoE; DLB-023; DLB-030; DLB-014/015/016; DLB-021; DD answers received in part on 1 October 2026 (DLB ABC Private Credit Diligence Responses, DLB-033)</t>
+          <t>DLB-031 internal QoE; DLB-023; DLB-030; DLB-014/015/016; DLB-021; DD answers received in part on 1 October 2026 (DLB Alder Point Credit Diligence Responses, DLB-033)</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="D532" s="7" t="inlineStr">
         <is>
-          <t>Compliance certificates in OP1-048, OP4-005, OP8-014; 2012 ABC Private Credit memo</t>
+          <t>Compliance certificates in OP1-048, OP4-005, OP8-014; 2012 Alder Point Credit memo</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="D544" s="7" t="inlineStr">
         <is>
-          <t>10-K/10-Q, clinic-level EBITDA, KPI files, ABC Private Credit IC and term sheet</t>
+          <t>10-K/10-Q, clinic-level EBITDA, KPI files, Alder Point Credit IC and term sheet</t>
         </is>
       </c>
       <c r="E544" s="7" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="D555" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit memo (CIM/QoE figures reproduced)</t>
+          <t>Alder Point Credit memo (CIM/QoE figures reproduced)</t>
         </is>
       </c>
       <c r="E555" s="7" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="F557" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA / FCCR</t>
+          <t>Alder Point Credit cash EBITDA / FCCR</t>
         </is>
       </c>
       <c r="G557" s="7" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="B625" s="7" t="inlineStr">
         <is>
-          <t>Comp sales Apr-20, revenue, as stated in ABC Private Credit's February 2021 Operator 1 transaction memo (OP1-033 p.31)</t>
+          <t>Comp sales Apr-20, revenue, as stated in Alder Point Credit's February 2021 Operator 1 transaction memo (OP1-033 p.31)</t>
         </is>
       </c>
       <c r="C625" s="15" t="n">
@@ -22482,7 +22482,7 @@
     <row r="817">
       <c r="A817" s="7" t="inlineStr">
         <is>
-          <t>Operator 3, ABC Private Credit chart</t>
+          <t>Operator 3, Alder Point Credit chart</t>
         </is>
       </c>
       <c r="B817" s="7" t="inlineStr">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="B865" s="7" t="inlineStr">
         <is>
-          <t>+3.0 / +2.3 / +0.3% ABC Private Credit-presented (OP1-048)</t>
+          <t>+3.0 / +2.3 / +0.3% Alder Point Credit-presented (OP1-048)</t>
         </is>
       </c>
       <c r="C865" s="7" t="inlineStr">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="B866" s="7" t="inlineStr">
         <is>
-          <t>+1.9% ABC Private Credit-presented (+1.8% OP4-005 panel)</t>
+          <t>+1.9% Alder Point Credit-presented (+1.8% OP4-005 panel)</t>
         </is>
       </c>
       <c r="C866" s="7" t="inlineStr">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="B872" s="7" t="inlineStr">
         <is>
-          <t>~5.8% ABC Private Credit memo (no definition)</t>
+          <t>~5.8% Alder Point Credit memo (no definition)</t>
         </is>
       </c>
       <c r="C872" s="7" t="inlineStr">
@@ -25805,7 +25805,7 @@
       </c>
       <c r="E944" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit "cash" 23.2 as printed, 24.9 corrected for a non-cash impairment (LTM)</t>
+          <t>Alder Point Credit "cash" 23.2 as printed, 24.9 corrected for a non-cash impairment (LTM)</t>
         </is>
       </c>
       <c r="F944" s="7" t="inlineStr">
@@ -25822,7 +25822,7 @@
     <row r="945" ht="91" customHeight="1">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>Source: note C-61; Deal A rows from the 10-K public series DLA_EBITDA_E1 and DLA_EBITDA_ADJ_PUB; Deal C rows DLC-0019, DLC-4434 (E1), DLC-4426, DLC-4430 (E3), DLC-4107, DLC-4443 (ABC Private Credit cash EBITDA). ADJ_SHARE = (top rung − E1) ÷ top rung; E6 = D3 cash EBITDA (top rung less recurring cash "one-time" items). Basis: E1 A; E2/E3/E6 PF; Deal A E2m is a reconstruction from company-published non-GAAP items; Operator 2 E1 is compliance-certificate basis [M]. Clinic base ALL (consolidated). The E6/top median of 0.84 is across the eleven Operator 4, Operator 8, Operator 6 and Operator 3 readings. Operator 8's E6 is built from its as-owned adjusted EBITDA (E2m, OP8-1880) and is set against that rung; its E3 (OP8-2409) is fully pro forma for acquisitions through May-26 and has no matching E6 (OP8-2015). Deal B's consolidated EBITDA includes DBW and is read in Part 06. Wellness clinic and emergency and specialty hospital context rows are in the same note, are not pooled and are shown in Exhibit 9.94 (adjustment share) and Exhibit 9.97 (cash EBITDA and add-back recurrence)</t>
+          <t>Source: note C-61; Deal A rows from the 10-K public series DLA_EBITDA_E1 and DLA_EBITDA_ADJ_PUB; Deal C rows DLC-0019, DLC-4434 (E1), DLC-4426, DLC-4430 (E3), DLC-4107, DLC-4443 (Alder Point Credit cash EBITDA). ADJ_SHARE = (top rung − E1) ÷ top rung; E6 = D3 cash EBITDA (top rung less recurring cash "one-time" items). Basis: E1 A; E2/E3/E6 PF; Deal A E2m is a reconstruction from company-published non-GAAP items; Operator 2 E1 is compliance-certificate basis [M]. Clinic base ALL (consolidated). The E6/top median of 0.84 is across the eleven Operator 4, Operator 8, Operator 6 and Operator 3 readings. Operator 8's E6 is built from its as-owned adjusted EBITDA (E2m, OP8-1880) and is set against that rung; its E3 (OP8-2409) is fully pro forma for acquisitions through May-26 and has no matching E6 (OP8-2015). Deal B's consolidated EBITDA includes DBW and is read in Part 06. Wellness clinic and emergency and specialty hospital context rows are in the same note, are not pooled and are shown in Exhibit 9.94 (adjustment share) and Exhibit 9.97 (cash EBITDA and add-back recurrence)</t>
         </is>
       </c>
     </row>
@@ -25836,7 +25836,7 @@
     <row r="948">
       <c r="A948" s="8" t="inlineStr">
         <is>
-          <t>EV ÷ EBITDA at entry (x) of closed or signed core platform and scale transactions, by EBITDA rung and synergy treatment, 2012 to 2026; deal documents supplied by ABC Private Credit</t>
+          <t>EV ÷ EBITDA at entry (x) of closed or signed core platform and scale transactions, by EBITDA rung and synergy treatment, 2012 to 2026; deal documents supplied by Alder Point Credit</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="B960" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit recap of GB Vet (Operator 2)</t>
+          <t>Alder Point Credit recap of GB Vet (Operator 2)</t>
         </is>
       </c>
       <c r="C960" s="7" t="inlineStr">
@@ -28145,7 +28145,7 @@
     <row r="1023">
       <c r="A1023" s="8" t="inlineStr">
         <is>
-          <t>Headline multiple (x), EV ($m), EBITDA rung, and leverage at close and after (x) for each platform transaction, Oct-14 to Aug-26; ABC Private Credit deal documents</t>
+          <t>Headline multiple (x), EV ($m), EBITDA rung, and leverage at close and after (x) for each platform transaction, Oct-14 to Aug-26; Alder Point Credit deal documents</t>
         </is>
       </c>
     </row>
@@ -28463,7 +28463,7 @@
       </c>
       <c r="B1030" s="7" t="inlineStr">
         <is>
-          <t>Operator 2 (GB Vet) — ABC Private Credit unitranche recap</t>
+          <t>Operator 2 (GB Vet) — Alder Point Credit unitranche recap</t>
         </is>
       </c>
       <c r="C1030" s="7" t="inlineStr">
@@ -28844,7 +28844,7 @@
       </c>
       <c r="G1037" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit unitranche Feb-25: LEV_ST-59 0.93x gross / 0.59x net (E5 TTM Sep-24 $8.3m; sources differ)</t>
+          <t>Alder Point Credit unitranche Feb-25: LEV_ST-59 0.93x gross / 0.59x net (E5 TTM Sep-24 $8.3m; sources differ)</t>
         </is>
       </c>
       <c r="H1037" s="7" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="B1041" s="7" t="inlineStr">
         <is>
-          <t>Operator 3 — Sponsor 5 (ABC Private Credit proposal)</t>
+          <t>Operator 3 — Sponsor 5 (Alder Point Credit proposal)</t>
         </is>
       </c>
       <c r="C1041" s="7" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="G1042" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit proposal: 2.25x gross / 1.97x net (E5 run-rate $8.8m, P)</t>
+          <t>Alder Point Credit proposal: 2.25x gross / 1.97x net (E5 run-rate $8.8m, P)</t>
         </is>
       </c>
       <c r="H1042" s="7" t="inlineStr">
@@ -30178,7 +30178,7 @@
     <row r="1080">
       <c r="A1080" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 1 in each of ABC Private Credit's six areas, with period, basis and reference; clinic sheets FY08 to LTM Nov-17, FY2019 audit</t>
+          <t>The figure the document gives for Operator 1 in each of Alder Point Credit's six areas, with period, basis and reference; clinic sheets FY08 to LTM Nov-17, FY2019 audit</t>
         </is>
       </c>
     </row>
@@ -30300,7 +30300,7 @@
       </c>
       <c r="B1086" s="7" t="inlineStr">
         <is>
-          <t>+8.8% on total clinic sales and +4.5% on retail in FY09. On the common clinic-level definition −0.3%, −1.6% and −4.0% in 2014–16, against +3.0%, +2.3% and +0.3% as presented to ABC Private Credit. On the common definition +0.4% in CY2019 and +7.0% in CY2022 (last of three in each) and −2.7% in 2020 (first of three).</t>
+          <t>+8.8% on total clinic sales and +4.5% on retail in FY09. On the common clinic-level definition −0.3%, −1.6% and −4.0% in 2014–16, against +3.0%, +2.3% and +0.3% as presented to Alder Point Credit. On the common definition +0.4% in CY2019 and +7.0% in CY2022 (last of three in each) and −2.7% in 2020 (first of three).</t>
         </is>
       </c>
       <c r="C1086" s="7" t="inlineStr">
@@ -30353,7 +30353,7 @@
     <row r="1091">
       <c r="A1091" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 2 and its Operator 10 seller chain in each of ABC Private Credit's six areas, with period, basis and reference; clinic data 2006 to LTM Mar-21, company decks to FY2025</t>
+          <t>The figure the document gives for Operator 2 and its Operator 10 seller chain in each of Alder Point Credit's six areas, with period, basis and reference; clinic data 2006 to LTM Mar-21, company decks to FY2025</t>
         </is>
       </c>
     </row>
@@ -30528,7 +30528,7 @@
     <row r="1102">
       <c r="A1102" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 4 (Operator 4 HoldCo) and Operator 9 in each of ABC Private Credit's six areas, with period, basis and reference; audits FY23 to FY25 and Q1-26; each cell names the company</t>
+          <t>The figure the document gives for Operator 4 (Operator 4 HoldCo) and Operator 9 in each of Alder Point Credit's six areas, with period, basis and reference; audits FY23 to FY25 and Q1-26; each cell names the company</t>
         </is>
       </c>
     </row>
@@ -30703,7 +30703,7 @@
     <row r="1113">
       <c r="A1113" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 5 in each of ABC Private Credit's six areas, with period, basis and reference; clinic tickets and units 2017 to Jun-23, clinic P&amp;L CY2020 to LTM Mar-23</t>
+          <t>The figure the document gives for Operator 5 in each of Alder Point Credit's six areas, with period, basis and reference; clinic tickets and units 2017 to Jun-23, clinic P&amp;L CY2020 to LTM Mar-23</t>
         </is>
       </c>
     </row>
@@ -30878,7 +30878,7 @@
     <row r="1124">
       <c r="A1124" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 6 in each of ABC Private Credit's six areas, with period, basis and reference; company data 2021 to TTM Mar-26, 31 add-ons</t>
+          <t>The figure the document gives for Operator 6 in each of Alder Point Credit's six areas, with period, basis and reference; company data 2021 to TTM Mar-26, 31 add-ons</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
     <row r="1135">
       <c r="A1135" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 3 in each of ABC Private Credit's six areas, with period, basis and reference; clinic datacube Apr-21 to Aug-25 (surviving clinics)</t>
+          <t>The figure the document gives for Operator 3 in each of Alder Point Credit's six areas, with period, basis and reference; clinic datacube Apr-21 to Aug-25 (surviving clinics)</t>
         </is>
       </c>
     </row>
@@ -31228,7 +31228,7 @@
     <row r="1146">
       <c r="A1146" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 7 State 05 segment in each of ABC Private Credit's six areas, with period, basis and reference; quality-of-earnings clinic P&amp;L Jan-23 to Jan-26, KPIs Jan-24 to Jun-26</t>
+          <t>The figure the document gives for Operator 7 State 05 segment in each of Alder Point Credit's six areas, with period, basis and reference; quality-of-earnings clinic P&amp;L Jan-23 to Jan-26, KPIs Jan-24 to Jun-26</t>
         </is>
       </c>
     </row>
@@ -31350,7 +31350,7 @@
       </c>
       <c r="B1152" s="7" t="inlineStr">
         <is>
-          <t>On the common definition +11.4% (2025) and +4.8% (LTM Jun-26), against about 5.8% in an ABC Private Credit memo with no stated definition. No comparable year before 2025, and in no ranking.</t>
+          <t>On the common definition +11.4% (2025) and +4.8% (LTM Jun-26), against about 5.8% in an Alder Point Credit memo with no stated definition. No comparable year before 2025, and in no ranking.</t>
         </is>
       </c>
       <c r="C1152" s="7" t="inlineStr">
@@ -31403,7 +31403,7 @@
     <row r="1157">
       <c r="A1157" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Operator 8 in each of ABC Private Credit's six areas, with period, basis and reference; clinic P&amp;L 2021 to LTM Mar-26, clinic-year volume 2021–24</t>
+          <t>The figure the document gives for Operator 8 in each of Alder Point Credit's six areas, with period, basis and reference; clinic P&amp;L 2021 to LTM Mar-26, clinic-year volume 2021–24</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31578,7 @@
     <row r="1168">
       <c r="A1168" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Deal A in each of ABC Private Credit's six areas, with period, basis and reference; Forms 10-K FY1996 to FY26 and Q1 FY27 10-Q, clinic EBITDA FY23–23, clinic KPIs FY20 to Q1 FY27; operating measures only</t>
+          <t>The figure the document gives for Deal A in each of Alder Point Credit's six areas, with period, basis and reference; Forms 10-K FY1996 to FY26 and Q1 FY27 10-Q, clinic EBITDA FY23–23, clinic KPIs FY20 to Q1 FY27; operating measures only</t>
         </is>
       </c>
     </row>
@@ -31753,7 +31753,7 @@
     <row r="1179">
       <c r="A1179" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Deal B's general practice and preventive operations (DLB) in each of ABC Private Credit's six areas, with period, basis and reference; clinic data Jan-23 to Aug-26; DBW excluded; operating measures only</t>
+          <t>The figure the document gives for Deal B's general practice and preventive operations (DLB) in each of Alder Point Credit's six areas, with period, basis and reference; clinic data Jan-23 to Aug-26; DBW excluded; operating measures only</t>
         </is>
       </c>
     </row>
@@ -31928,7 +31928,7 @@
     <row r="1190">
       <c r="A1190" s="8" t="inlineStr">
         <is>
-          <t>The figure the document gives for Deal C in each of ABC Private Credit's six areas, with period, basis and reference; 2025 audit, site-level database Jan-22 to Jul-26, company KPIs; operating measures only</t>
+          <t>The figure the document gives for Deal C in each of Alder Point Credit's six areas, with period, basis and reference; 2025 audit, site-level database Jan-22 to Jul-26, company KPIs; operating measures only</t>
         </is>
       </c>
     </row>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="B1204" s="7" t="inlineStr">
         <is>
-          <t>FY24 / FY25: 19.4% / 26.8% on the clinics that survive to FY26 vs 27.2% / 34.3% on all clinics open at each year-end; FY26 28.7% on both; FY26 19.5% with co-op allocated to clinics at 5.15% of clinic sales (ABC Private Credit's basis; Part 05 section E)</t>
+          <t>FY24 / FY25: 19.4% / 26.8% on the clinics that survive to FY26 vs 27.2% / 34.3% on all clinics open at each year-end; FY26 28.7% on both; FY26 19.5% with co-op allocated to clinics at 5.15% of clinic sales (Alder Point Credit's basis; Part 05 section E)</t>
         </is>
       </c>
       <c r="C1204" s="7" t="inlineStr">
@@ -32991,12 +32991,12 @@
       </c>
       <c r="E1242" s="7" t="inlineStr">
         <is>
-          <t>6.2× 2018, rung n/s, A; 5.15× ABC Private Credit recap 2025, P (QL1-1729, QL1-1722)</t>
+          <t>6.2× 2018, rung n/s, A; 5.15× Alder Point Credit recap 2025, P (QL1-1729, QL1-1722)</t>
         </is>
       </c>
       <c r="F1242" s="7" t="inlineStr">
         <is>
-          <t>1L 3.69× gross on ABC Private Credit E5 LTM Oct-25, P; LV3 3.05× on E4 PF (QL1-1655, QL1-0498)</t>
+          <t>1L 3.69× gross on Alder Point Credit E5 LTM Oct-25, P; LV3 3.05× on E4 PF (QL1-1655, QL1-0498)</t>
         </is>
       </c>
     </row>
@@ -33669,7 +33669,7 @@
       </c>
       <c r="J1261" s="7" t="inlineStr">
         <is>
-          <t>0.76 LTM Sep-25 (ABC Private Credit cash EBITDA)</t>
+          <t>0.76 LTM Sep-25 (Alder Point Credit cash EBITDA)</t>
         </is>
       </c>
       <c r="K1261" s="7" t="inlineStr">
@@ -35537,7 +35537,7 @@
       </c>
       <c r="B1323" s="7" t="inlineStr">
         <is>
-          <t>Wellness Clinic Operator 2 — ABC Private Credit refinancing proposal</t>
+          <t>Wellness Clinic Operator 2 — Alder Point Credit refinancing proposal</t>
         </is>
       </c>
       <c r="C1323" s="7" t="inlineStr">
@@ -35564,7 +35564,7 @@
       </c>
       <c r="B1324" s="7" t="inlineStr">
         <is>
-          <t>Wellness Clinic Operator 1 — 2025 recapitalisation (ABC Private Credit memo of 22 December 2025)</t>
+          <t>Wellness Clinic Operator 1 — 2025 recapitalisation (Alder Point Credit memo of 22 December 2025)</t>
         </is>
       </c>
       <c r="C1324" s="7" t="inlineStr">
@@ -37556,7 +37556,7 @@
     <row r="1420">
       <c r="A1420" s="7" t="inlineStr">
         <is>
-          <t>Clinic EBITDA including co-op allocated at 5.15% of clinic sales (ABC Private Credit's basis), FY26 (A; the 824 clinics kept after the second round PF)</t>
+          <t>Clinic EBITDA including co-op allocated at 5.15% of clinic sales (Alder Point Credit's basis), FY26 (A; the 824 clinics kept after the second round PF)</t>
         </is>
       </c>
       <c r="B1420" s="7" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="D1472" s="7" t="inlineStr">
         <is>
-          <t>Four-wall level and loss share (Operator 1 D1.1 R-CASH to Nov-17 vs Deal A R-OPONLY FY23–23: different rent code, no overlap); SSS (Operator 1 CLOSE-FWD 2019–22 vs Deal A survivor CLOSE-RETRO; Operator 1 2023–25 is an undefined SSS_ST-59 from the ABC Private Credit chart); volume (Operator 1 pharmacy units, not traffic, ending Nov-17); valuation (E4 platform multiples vs Deal A public EV on E1)</t>
+          <t>Four-wall level and loss share (Operator 1 D1.1 R-CASH to Nov-17 vs Deal A R-OPONLY FY23–23: different rent code, no overlap); SSS (Operator 1 CLOSE-FWD 2019–22 vs Deal A survivor CLOSE-RETRO; Operator 1 2023–25 is an undefined SSS_ST-59 from the Alder Point Credit chart); volume (Operator 1 pharmacy units, not traffic, ending Nov-17); valuation (E4 platform multiples vs Deal A public EV on E1)</t>
         </is>
       </c>
     </row>
@@ -39075,7 +39075,7 @@
       </c>
       <c r="B1497" s="7" t="inlineStr">
         <is>
-          <t>The panel's Operator 1 column equals ABC Private Credit's own OP1-048 chart to rounding, so it is not an independent source, and that series is contradicted by Operator 1 clinic-level SSS_CD in 2012, 2014–16 and 2020 (−0.2%, −0.3%, −1.6%, −4.0%, −2.7% against the panel's +3%, +3%, +3%, 0%, +2%) (OP1-5128, OP1-5130..5132, OP1-8857; OP4-0559..0567). The panel's Deal A 2013 value (−4%, OP4-0576) is a transcription error against the 10-K's −0.4% (DLA-0347). Deal A's public comp is SSS_ST-59; Operator 1' is SSS_CD (CLOSE-FWD) to 2022 and undefined SSS_ST-59 from 2023</t>
+          <t>The panel's Operator 1 column equals Alder Point Credit's own OP1-048 chart to rounding, so it is not an independent source, and that series is contradicted by Operator 1 clinic-level SSS_CD in 2012, 2014–16 and 2020 (−0.2%, −0.3%, −1.6%, −4.0%, −2.7% against the panel's +3%, +3%, +3%, 0%, +2%) (OP1-5128, OP1-5130..5132, OP1-8857; OP4-0559..0567). The panel's Deal A 2013 value (−4%, OP4-0576) is a transcription error against the 10-K's −0.4% (DLA-0347). Deal A's public comp is SSS_ST-59; Operator 1' is SSS_CD (CLOSE-FWD) to 2022 and undefined SSS_ST-59 from 2023</t>
         </is>
       </c>
       <c r="C1497" s="7" t="inlineStr">
@@ -40423,7 +40423,7 @@
       </c>
       <c r="D1559" s="7" t="inlineStr">
         <is>
-          <t>FY25 0.99 (E3 Accounting Firm 2 $24.2m, DLB-3901), 1.03 (Accounting Firm 2 $18.5m, DLB-3900), 1.13 (post-audit $10.1m, DLB-5250), E1 −$3.2m (DLB-3866); LTM Jul-26 0.78 (post-audit $14.0m, DLB-5599) / 0.76 (ABC Private Credit E5, DLB-6300), E1 $1.22m (DLB-5644)</t>
+          <t>FY25 0.99 (E3 Accounting Firm 2 $24.2m, DLB-3901), 1.03 (Accounting Firm 2 $18.5m, DLB-3900), 1.13 (post-audit $10.1m, DLB-5250), E1 −$3.2m (DLB-3866); LTM Jul-26 0.78 (post-audit $14.0m, DLB-5599) / 0.76 (Alder Point Credit E5, DLB-6300), E1 $1.22m (DLB-5644)</t>
         </is>
       </c>
       <c r="E1559" s="7" t="inlineStr">
@@ -40450,7 +40450,7 @@
       </c>
       <c r="D1560" s="7" t="inlineStr">
         <is>
-          <t>FY25 0.46 (A6-P5-008..010); LTM Jul-26 0.59 / 0.52 / 0.37 on post-audit pro forma / ABC Private Credit E5 / E2 (DLB-5645)</t>
+          <t>FY25 0.46 (A6-P5-008..010); LTM Jul-26 0.59 / 0.52 / 0.37 on post-audit pro forma / Alder Point Credit E5 / E2 (DLB-5645)</t>
         </is>
       </c>
       <c r="E1560" s="7" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="D1562" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash $5.68m ÷ E5 0.43; ÷ post-audit pro forma 0.34 (DLB-6300/6302; DLB-5599)</t>
+          <t>Alder Point Credit cash $5.68m ÷ E5 0.43; ÷ post-audit pro forma 0.34 (DLB-6300/6302; DLB-5599)</t>
         </is>
       </c>
       <c r="E1562" s="7" t="inlineStr">
@@ -40543,7 +40543,7 @@
     <row r="1564" ht="39" customHeight="1">
       <c r="A1564" s="9" t="inlineStr">
         <is>
-          <t>Source: Rows as shown in each cell; Deal B Financing Model Jul-26 RF (DLB-008), QoE Workbook (DLB-022) and ABC Private Credit model vRF 09 (DLB-027); peer tables as referenced; note C-39 · Basis: Adjusted EBITDA rungs as labelled (E1 reported; E2, E3 and E5 adjusted, PF); Deal B's EBITDA rungs are consolidated, DBW included (DBW is read in Part 06 section F); maintenance capex is each company's own split [M]; peers' top rungs differ</t>
+          <t>Source: Rows as shown in each cell; Deal B Financing Model Jul-26 RF (DLB-008), QoE Workbook (DLB-022) and Alder Point Credit model vRF 09 (DLB-027); peer tables as referenced; note C-39 · Basis: Adjusted EBITDA rungs as labelled (E1 reported; E2, E3 and E5 adjusted, PF); Deal B's EBITDA rungs are consolidated, DBW included (DBW is read in Part 06 section F); maintenance capex is each company's own split [M]; peers' top rungs differ</t>
         </is>
       </c>
     </row>
@@ -40805,7 +40805,7 @@
       </c>
       <c r="B1583" s="7" t="inlineStr">
         <is>
-          <t>Wellness Clinic Operator 2 add-ons 4.4x at close (A, as stated by the company [M]; QL2-1038); QL1 2025 5.15x (P, ABC Private Credit QoE; QL1-1722); JLI franchisees 5.8x (2023) and 6.3x LOI (2024) (rung n/s; QL1-1736/1735); QL1 2018 6.2x (QL1-1729)</t>
+          <t>Wellness Clinic Operator 2 add-ons 4.4x at close (A, as stated by the company [M]; QL2-1038); QL1 2025 5.15x (P, Alder Point Credit QoE; QL1-1722); JLI franchisees 5.8x (2023) and 6.3x LOI (2024) (rung n/s; QL1-1736/1735); QL1 2018 6.2x (QL1-1729)</t>
         </is>
       </c>
       <c r="C1583" s="7" t="inlineStr">
@@ -42200,7 +42200,7 @@
       </c>
       <c r="B1666" s="7" t="inlineStr">
         <is>
-          <t>$4.7m ($1.4m ex $3.4m non-cash earn-out credit; Accounting Firm 1 "reported" $4.0m, as quoted from the QoE in ABC Private Credit's Internal Diligence Exhibits (the QoE itself was not supplied), omits a $1.0m impairment)</t>
+          <t>$4.7m ($1.4m ex $3.4m non-cash earn-out credit; Accounting Firm 1 "reported" $4.0m, as quoted from the QoE in Alder Point Credit's Internal Diligence Exhibits (the QoE itself was not supplied), omits a $1.0m impairment)</t>
         </is>
       </c>
       <c r="C1666" s="7" t="inlineStr">
@@ -42229,7 +42229,7 @@
     <row r="1668">
       <c r="A1668" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit underwriting (E5), LTM Sep-26E (P) / sponsor pro forma, LTM Sep-26E (P)</t>
+          <t>Alder Point Credit underwriting (E5), LTM Sep-26E (P) / sponsor pro forma, LTM Sep-26E (P)</t>
         </is>
       </c>
       <c r="B1668" s="7" t="inlineStr">
@@ -42263,7 +42263,7 @@
     <row r="1670">
       <c r="A1670" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, LTM Apr-26</t>
+          <t>Alder Point Credit cash EBITDA, LTM Apr-26</t>
         </is>
       </c>
       <c r="B1670" s="7" t="inlineStr">
@@ -43519,7 +43519,7 @@
     <row r="1724">
       <c r="A1724" s="7" t="inlineStr">
         <is>
-          <t>E5 ABC Private Credit, LTM Sep-26E (P)</t>
+          <t>E5 Alder Point Credit, LTM Sep-26E (P)</t>
         </is>
       </c>
       <c r="B1724" s="7" t="inlineStr">
@@ -43585,7 +43585,7 @@
     <row r="1727">
       <c r="A1727" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA (EB_CASH_ST-59, ABC Private Credit), LTM Apr-26 — not E6</t>
+          <t>Alder Point Credit cash EBITDA (EB_CASH_ST-59, Alder Point Credit), LTM Apr-26 — not E6</t>
         </is>
       </c>
       <c r="B1727" s="7" t="inlineStr">
@@ -44147,7 +44147,7 @@
     <row r="1756">
       <c r="A1756" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 LTM Sep-26 $71.7m (P), at close</t>
+          <t>Alder Point Credit E5 LTM Sep-26 $71.7m (P), at close</t>
         </is>
       </c>
       <c r="B1756" s="7" t="inlineStr">
@@ -44204,7 +44204,7 @@
       </c>
       <c r="F1757" s="7" t="inlineStr">
         <is>
-          <t>DLA-023 (LW draft term sheet (21 September 2026)), Financial Covenants; inputs from DLA-024 (ABC Private Credit Deal A Model v24) [I]</t>
+          <t>DLA-023 (LW draft term sheet (21 September 2026)), Financial Covenants; inputs from DLA-024 (Alder Point Credit Deal A Model v24) [I]</t>
         </is>
       </c>
     </row>
@@ -44226,7 +44226,7 @@
       </c>
       <c r="D1758" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit "rent-adjusted" 4.64x counts finance leases twice; ABC Private Credit v24 covenant line 4.46x (FQ3'27, net, capped cash); reading (a) 3.81x, and 4.47x if the $17.4m of gains is excluded</t>
+          <t>Alder Point Credit "rent-adjusted" 4.64x counts finance leases twice; Alder Point Credit v24 covenant line 4.46x (FQ3'27, net, capped cash); reading (a) 3.81x, and 4.47x if the $17.4m of gains is excluded</t>
         </is>
       </c>
       <c r="E1758" s="7" t="inlineStr">
@@ -44243,7 +44243,7 @@
     <row r="1759" ht="65" customHeight="1">
       <c r="A1759" s="9" t="inlineStr">
         <is>
-          <t>Source: note C-81 (FY2026, FY2026 ex-gains, LTM Jun-26 rows); Exhibit 9.76; fact rows as listed; DLA-023 (LW draft term sheet (21 September 2026)), Financial Covenants, for the covenant constructions. LV1 = bank and mortgage debt; LV3 adds finance leases and financing obligations ($194.3m FY26, DLA-0471; $196.6m Jun-26, A8-P5-089); LV5_6X adds 6 × operating-lease cash payments over E1 + rent; LV6 adds supplier finance. LTM LV5/LV6 on E1 are not computable because the 10-Q omits quarterly operating-lease cash payments [note C-81]. Charted in Exhibit 9.154 · Basis: Audited rungs A; company EBITDA PF; ABC Private Credit's EBITDA and covenant constructions P</t>
+          <t>Source: note C-81 (FY2026, FY2026 ex-gains, LTM Jun-26 rows); Exhibit 9.76; fact rows as listed; DLA-023 (LW draft term sheet (21 September 2026)), Financial Covenants, for the covenant constructions. LV1 = bank and mortgage debt; LV3 adds finance leases and financing obligations ($194.3m FY26, DLA-0471; $196.6m Jun-26, A8-P5-089); LV5_6X adds 6 × operating-lease cash payments over E1 + rent; LV6 adds supplier finance. LTM LV5/LV6 on E1 are not computable because the 10-Q omits quarterly operating-lease cash payments [note C-81]. Charted in Exhibit 9.154 · Basis: Audited rungs A; company EBITDA PF; Alder Point Credit's EBITDA and covenant constructions P</t>
         </is>
       </c>
     </row>
@@ -44332,7 +44332,7 @@
     <row r="1768">
       <c r="A1768" s="8" t="inlineStr">
         <is>
-          <t>Minimum quarter-average liquidity, $m, and the quarter it falls in, October 2026 to September 2030; management plan as in ABC Private Credit model v24; covenant $21.5m of average daily Liquidity</t>
+          <t>Minimum quarter-average liquidity, $m, and the quarter it falls in, October 2026 to September 2030; management plan as in Alder Point Credit model v24; covenant $21.5m of average daily Liquidity</t>
         </is>
       </c>
     </row>
@@ -44361,7 +44361,7 @@
     <row r="1770">
       <c r="A1770" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model: $4.3m, April 2027 to March 2028</t>
+          <t>Alder Point Credit's model: $4.3m, April 2027 to March 2028</t>
         </is>
       </c>
       <c r="B1770" s="7" t="inlineStr">
@@ -44441,7 +44441,7 @@
     <row r="1774">
       <c r="A1774" s="7" t="inlineStr">
         <is>
-          <t>Lead case with EBITDA 9% below ABC Private Credit's model and no closure benefit</t>
+          <t>Lead case with EBITDA 9% below Alder Point Credit's model and no closure benefit</t>
         </is>
       </c>
       <c r="B1774" s="7" t="inlineStr">
@@ -44455,7 +44455,7 @@
     <row r="1775" ht="65" customHeight="1">
       <c r="A1775" s="9" t="inlineStr">
         <is>
-          <t>Source: CreditSwan monthly model of the proposed facilities (C-FIN-1, C-FIN-2); ABC Private Credit Deal A Model v24, MODEL OUTPUT rows 13 to 28, 38, 103, 152; LW draft term sheet (21 September 2026), Credit Facilities, Use of Proceeds, Financial Covenants; Alpha - FY27 Clinic Closure Data, Summary!J33, J43 · Basis: P (projection on management's plan); monthly points, quarter average by daily interpolation between month-ends · Assumption: Every case carries $4.3m of professional fees, $25.5m of letters of credit, finance-lease interest charged to cash and the $7.4m December 2026 dividend. The shortfall is a uniform reduction of EBITDA in every period</t>
+          <t>Source: CreditSwan monthly model of the proposed facilities (C-FIN-1, C-FIN-2); Alder Point Credit Deal A Model v24, MODEL OUTPUT rows 13 to 28, 38, 103, 152; LW draft term sheet (21 September 2026), Credit Facilities, Use of Proceeds, Financial Covenants; Alpha - FY27 Clinic Closure Data, Summary!J33, J43 · Basis: P (projection on management's plan); monthly points, quarter average by daily interpolation between month-ends · Assumption: Every case carries $4.3m of professional fees, $25.5m of letters of credit, finance-lease interest charged to cash and the $7.4m December 2026 dividend. The shortfall is a uniform reduction of EBITDA in every period</t>
         </is>
       </c>
     </row>
@@ -44469,7 +44469,7 @@
     <row r="1778">
       <c r="A1778" s="8" t="inlineStr">
         <is>
-          <t>Refinancing capacity at maturity (September 2030) on observed anchors, by pairing of need and capacity, $m; LW draft term sheet (21 September 2026) and ABC Private Credit's Deal A model v24</t>
+          <t>Refinancing capacity at maturity (September 2030) on observed anchors, by pairing of need and capacity, $m; LW draft term sheet (21 September 2026) and Alder Point Credit's Deal A model v24</t>
         </is>
       </c>
     </row>
@@ -44518,7 +44518,7 @@
       </c>
       <c r="C1780" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit-model downside EBITDA $93.3m (P)</t>
+          <t>Alder Point Credit-model downside EBITDA $93.3m (P)</t>
         </is>
       </c>
       <c r="D1780" s="13" t="n">
@@ -44894,7 +44894,7 @@
     <row r="1793" ht="78" customHeight="1">
       <c r="A1793" s="9" t="inlineStr">
         <is>
-          <t>Source: Needs, cash flow available for debt service and downside EBITDA from the CreditSwan monthly model (C-FIN-1, C-FIN-3); multiples OP6-0031 (3.81x), OP1-7357 (4.27x), P5-S001 (5.97x), 8 closed gross first-lien prints from 3 platforms; spreads OP2-4336 (S+383), OP7-1164 (S+422), DLA-5593 (S+528), A8-S012 (S+534); SOFR 4.10% from ABC Private Credit Deal A Model v24, MODEL OUTPUT!L118; EBITDA rungs DLA-5864, A8-P5-092, DLA-0317, A8-P5-096 · Basis: Need P; actual rungs A and PF, held flat; downside EBITDA P. All results [I] · Assumption: Leverage leg = (multiple × EBITDA − $112.2m of finance leases at maturity) × 0.85. Coverage leg = cash flow available for debt service ÷ (cover × (SOFR + spread)) × 0.85. Need = bank debt less cash above a $13m reserve. Base path = lead case; downside = EBITDA 9% below ABC Private Credit's model in every period, no closure benefit</t>
+          <t>Source: Needs, cash flow available for debt service and downside EBITDA from the CreditSwan monthly model (C-FIN-1, C-FIN-3); multiples OP6-0031 (3.81x), OP1-7357 (4.27x), P5-S001 (5.97x), 8 closed gross first-lien prints from 3 platforms; spreads OP2-4336 (S+383), OP7-1164 (S+422), DLA-5593 (S+528), A8-S012 (S+534); SOFR 4.10% from Alder Point Credit Deal A Model v24, MODEL OUTPUT!L118; EBITDA rungs DLA-5864, A8-P5-092, DLA-0317, A8-P5-096 · Basis: Need P; actual rungs A and PF, held flat; downside EBITDA P. All results [I] · Assumption: Leverage leg = (multiple × EBITDA − $112.2m of finance leases at maturity) × 0.85. Coverage leg = cash flow available for debt service ÷ (cover × (SOFR + spread)) × 0.85. Need = bank debt less cash above a $13m reserve. Base path = lead case; downside = EBITDA 9% below Alder Point Credit's model in every period, no closure benefit</t>
         </is>
       </c>
     </row>
@@ -45384,7 +45384,7 @@
     <row r="1820" ht="30" customHeight="1">
       <c r="A1820" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.162 — Deal B needs EBITDA of $16.1–16.6m to refinance its term loan and delayed-draw loan at 4.3x in December 2030, against $11.16m on ABC Private Credit's measure today, and the near-term batch is $8.8–11.8m short of committed sources</t>
+          <t>Exhibit 9.162 — Deal B needs EBITDA of $16.1–16.6m to refinance its term loan and delayed-draw loan at 4.3x in December 2030, against $11.16m on Alder Point Credit's measure today, and the near-term batch is $8.8–11.8m short of committed sources</t>
         </is>
       </c>
     </row>
@@ -45450,12 +45450,12 @@
       </c>
       <c r="E1823" s="7" t="inlineStr">
         <is>
-          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit), 0.61x (ABC Private Credit E5), 0.34x (E2) (DLB-9603..9607)</t>
+          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit), 0.61x (Alder Point Credit E5), 0.34x (E2) (DLB-9603..9607)</t>
         </is>
       </c>
       <c r="F1823" s="7" t="inlineStr">
         <is>
-          <t>1.08x on $14.6m; 0.73x with DDTL drawn; 0.02x on ABC Private Credit cash</t>
+          <t>1.08x on $14.6m; 0.73x with DDTL drawn; 0.02x on Alder Point Credit cash</t>
         </is>
       </c>
     </row>
@@ -45477,12 +45477,12 @@
       </c>
       <c r="D1824" s="7" t="inlineStr">
         <is>
-          <t>LV4 at close 7.59x on ABC Private Credit E5 (DLB-9355); 5.99x on $14.77m (DLB-9373)</t>
+          <t>LV4 at close 7.59x on Alder Point Credit E5 (DLB-9355); 5.99x on $14.77m (DLB-9373)</t>
         </is>
       </c>
       <c r="E1824" s="7" t="inlineStr">
         <is>
-          <t>7.85–8.25x on ABC Private Credit E5 and 6.00–6.35x on $14.77m, after and before scheduled term-loan and seller-note principal</t>
+          <t>7.85–8.25x on Alder Point Credit E5 and 6.00–6.35x on $14.77m, after and before scheduled term-loan and seller-note principal</t>
         </is>
       </c>
       <c r="F1824" s="7" t="inlineStr">
@@ -45514,7 +45514,7 @@
       </c>
       <c r="E1825" s="7" t="inlineStr">
         <is>
-          <t>EBITDA of $16.1–16.6m refinances the term loan and DDTL at 4.3x; $18.6–24.6m refinances them plus HoldCo at 5.4–7.2x (revolver excluded); against $11.16m ABC Private Credit E5 and $13.79m post-audit today</t>
+          <t>EBITDA of $16.1–16.6m refinances the term loan and DDTL at 4.3x; $18.6–24.6m refinances them plus HoldCo at 5.4–7.2x (revolver excluded); against $11.16m Alder Point Credit E5 and $13.79m post-audit today</t>
         </is>
       </c>
       <c r="F1825" s="7" t="inlineStr"/>
@@ -45550,7 +45550,7 @@
     <row r="1827" ht="39" customHeight="1">
       <c r="A1827" s="9" t="inlineStr">
         <is>
-          <t>Source: DLB-5662; DLB-5668; DLB-6246; DLB-6351; DLB-9111; DLB-9355; DLB-9373; DLB-9603..9611; peers OP7-1304, OP6-0141, OP8-2547, OP8-2819/2367, OP1-10730/10738; Exhibit 4.09; notes C-80 and C-FIN-5 · Basis: P for the structure at close and every forward figure; peer anchors as printed (A, PF or P). The last column holds only figures printed in the borrower's and ABC Private Credit's models</t>
+          <t>Source: DLB-5662; DLB-5668; DLB-6246; DLB-6351; DLB-9111; DLB-9355; DLB-9373; DLB-9603..9611; peers OP7-1304, OP6-0141, OP8-2547, OP8-2819/2367, OP1-10730/10738; Exhibit 4.09; notes C-80 and C-FIN-5 · Basis: P for the structure at close and every forward figure; peer anchors as printed (A, PF or P). The last column holds only figures printed in the borrower's and Alder Point Credit's models</t>
         </is>
       </c>
     </row>
@@ -45776,7 +45776,7 @@
     <row r="1842" ht="45" customHeight="1">
       <c r="A1842" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.164 — Option Two covers its fixed charges only on EBITDA that includes forecast months (0.96x on ABC Private Credit's $29.4m); on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back it computes at 0.77x, against a $26.0m cash breakeven (LTM April and September 2026E)</t>
+          <t>Exhibit 9.164 — Option Two covers its fixed charges only on EBITDA that includes forecast months (0.96x on Alder Point Credit's $29.4m); on Alder Point Credit's cash EBITDA with the $1.0m non-cash impairment added back it computes at 0.77x, against a $26.0m cash breakeven (LTM April and September 2026E)</t>
         </is>
       </c>
     </row>
@@ -45834,7 +45834,7 @@
     <row r="1846">
       <c r="A1846" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA as printed $23.2m (LTM Apr-26, PF)</t>
+          <t>Alder Point Credit cash EBITDA as printed $23.2m (LTM Apr-26, PF)</t>
         </is>
       </c>
       <c r="B1846" s="7" t="inlineStr">
@@ -45856,7 +45856,7 @@
     <row r="1847">
       <c r="A1847" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m (LTM Apr-26, PF)</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m (LTM Apr-26, PF)</t>
         </is>
       </c>
       <c r="B1847" s="7" t="inlineStr">
@@ -45878,7 +45878,7 @@
     <row r="1848">
       <c r="A1848" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit $29.4m (E5, LTM Sep-26E, P)</t>
+          <t>Alder Point Credit $29.4m (E5, LTM Sep-26E, P)</t>
         </is>
       </c>
       <c r="B1848" s="7" t="inlineStr">
@@ -45951,7 +45951,7 @@
     <row r="1853" ht="45" customHeight="1">
       <c r="A1853" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 9.165 — At maturity in September 2032 Option Two leaves an $7.5m gap at the 4.3x median on ABC Private Credit's $29.4m growing 1.0% a year, and $59.3m on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); flat $29.4m clears only at 5.18x</t>
+          <t>Exhibit 9.165 — At maturity in September 2032 Option Two leaves an $7.5m gap at the 4.3x median on Alder Point Credit's $29.4m growing 1.0% a year, and $59.3m on Alder Point Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); flat $29.4m clears only at 5.18x</t>
         </is>
       </c>
     </row>
@@ -46245,7 +46245,7 @@
     <row r="1862">
       <c r="A1862" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1862" s="7" t="inlineStr">
@@ -46283,7 +46283,7 @@
     <row r="1863">
       <c r="A1863" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1863" s="7" t="inlineStr">
@@ -46321,7 +46321,7 @@
     <row r="1864">
       <c r="A1864" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1864" s="7" t="inlineStr">
@@ -46359,7 +46359,7 @@
     <row r="1865">
       <c r="A1865" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1865" s="7" t="inlineStr">
@@ -46397,7 +46397,7 @@
     <row r="1866">
       <c r="A1866" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1866" s="7" t="inlineStr">
@@ -46435,7 +46435,7 @@
     <row r="1867">
       <c r="A1867" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m</t>
         </is>
       </c>
       <c r="B1867" s="7" t="inlineStr">
@@ -46546,7 +46546,7 @@
       </c>
       <c r="B1873" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Alder Point Credit E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1873" s="7" t="inlineStr">
@@ -46587,7 +46587,7 @@
       </c>
       <c r="B1874" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Alder Point Credit E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1874" s="7" t="inlineStr">
@@ -46628,7 +46628,7 @@
       </c>
       <c r="B1875" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Alder Point Credit E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1875" s="7" t="inlineStr">
@@ -46669,7 +46669,7 @@
       </c>
       <c r="B1876" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Alder Point Credit E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1876" s="7" t="inlineStr">
@@ -46708,7 +46708,7 @@
       </c>
       <c r="B1877" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Alder Point Credit E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1877" s="7" t="inlineStr">
@@ -46747,7 +46747,7 @@
       </c>
       <c r="B1878" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Alder Point Credit E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1878" s="7" t="inlineStr">
@@ -46786,7 +46786,7 @@
       </c>
       <c r="B1879" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Alder Point Credit E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1879" s="7" t="inlineStr">
@@ -46825,7 +46825,7 @@
       </c>
       <c r="B1880" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $29.4m, flat</t>
+          <t>Alder Point Credit E5 $29.4m, flat</t>
         </is>
       </c>
       <c r="C1880" s="7" t="inlineStr">
@@ -46864,7 +46864,7 @@
       </c>
       <c r="B1881" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1881" s="7" t="inlineStr">
@@ -46905,7 +46905,7 @@
       </c>
       <c r="B1882" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1882" s="7" t="inlineStr">
@@ -46946,7 +46946,7 @@
       </c>
       <c r="B1883" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1883" s="7" t="inlineStr">
@@ -46987,7 +46987,7 @@
       </c>
       <c r="B1884" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1884" s="7" t="inlineStr">
@@ -47026,7 +47026,7 @@
       </c>
       <c r="B1885" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1885" s="7" t="inlineStr">
@@ -47065,7 +47065,7 @@
       </c>
       <c r="B1886" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1886" s="7" t="inlineStr">
@@ -47104,7 +47104,7 @@
       </c>
       <c r="B1887" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1887" s="7" t="inlineStr">
@@ -47143,7 +47143,7 @@
       </c>
       <c r="B1888" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
+          <t>Alder Point Credit cash EBITDA, $1.0m impairment added back, $24.9m, +1.0%/yr</t>
         </is>
       </c>
       <c r="C1888" s="7" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="D1899" s="7" t="inlineStr">
         <is>
-          <t>Option One 5.30× on ABC Private Credit E5, LTM Sep-26E (DLC-4872, P); Option Two 5.96× on ABC Private Credit E5 (DLC-4725, P; equal to Option One's LV4 with the $21m sponsor debt, DLC-4878) and 5.61× on the sponsor's $32.3m (DLC-4711)</t>
+          <t>Option One 5.30× on Alder Point Credit E5, LTM Sep-26E (DLC-4872, P); Option Two 5.96× on Alder Point Credit E5 (DLC-4725, P; equal to Option One's LV4 with the $21m sponsor debt, DLC-4878) and 5.61× on the sponsor's $32.3m (DLC-4711)</t>
         </is>
       </c>
       <c r="E1899" s="7" t="inlineStr">
@@ -47402,7 +47402,7 @@
       </c>
       <c r="D1900" s="7" t="inlineStr">
         <is>
-          <t>14.8× sell-side (DLC-012-000514) / 16.59× ABC Private Credit (DLC-012-000515); LTM Sep-26E contains forecast months, P</t>
+          <t>14.8× sell-side (DLC-012-000514) / 16.59× Alder Point Credit (DLC-012-000515); LTM Sep-26E contains forecast months, P</t>
         </is>
       </c>
       <c r="E1900" s="7" t="inlineStr">
@@ -47428,7 +47428,7 @@
     <row r="1904">
       <c r="A1904" s="8" t="inlineStr">
         <is>
-          <t>Sensitivities that bear on the Deal A financing, set against observed ranges, on CreditSwan's monthly model of the LW draft term sheet (21 September 2026) and ABC Private Credit's Deal A model v24; liquidity in $m of minimum quarter-average, refinancing at September 2030</t>
+          <t>Sensitivities that bear on the Deal A financing, set against observed ranges, on CreditSwan's monthly model of the LW draft term sheet (21 September 2026) and Alder Point Credit's Deal A model v24; liquidity in $m of minimum quarter-average, refinancing at September 2030</t>
         </is>
       </c>
     </row>
@@ -47472,7 +47472,7 @@
       </c>
       <c r="C1906" s="7" t="inlineStr">
         <is>
-          <t>The term sheet limits the loan to the supplier-finance unwind and lets revolver loans fund it only if the loan is unavailable (LW draft term sheet (21 September 2026), Use of Proceeds); ABC Private Credit's model draws $86m and holds revolver loans at $67m (MODEL OUTPUT!D33:H34, C41:I41)</t>
+          <t>The term sheet limits the loan to the supplier-finance unwind and lets revolver loans fund it only if the loan is unavailable (LW draft term sheet (21 September 2026), Use of Proceeds); Alder Point Credit's model draws $86m and holds revolver loans at $67m (MODEL OUTPUT!D33:H34, C41:I41)</t>
         </is>
       </c>
       <c r="D1906" s="7" t="inlineStr">
@@ -47494,12 +47494,12 @@
       </c>
       <c r="B1907" s="7" t="inlineStr">
         <is>
-          <t>$36.6m spread over the remaining lease terms ($39.6m on ABC Private Credit's $4.3m figure); $21.0m inside four quarters</t>
+          <t>$36.6m spread over the remaining lease terms ($39.6m on Alder Point Credit's $4.3m figure); $21.0m inside four quarters</t>
         </is>
       </c>
       <c r="C1907" s="7" t="inlineStr">
         <is>
-          <t>Workbook: costs run to lease end, 42.1 months on average (Summary!J33, B49); ABC Private Credit's model: $4.3m, April 2027 to March 2028 (MODEL OUTPUT!F20:I20); the Diligence &amp; Structure Update (p.11) shows about $4.3m a year on a lease average of about five years</t>
+          <t>Workbook: costs run to lease end, 42.1 months on average (Summary!J33, B49); Alder Point Credit's model: $4.3m, April 2027 to March 2028 (MODEL OUTPUT!F20:I20); the Diligence &amp; Structure Update (p.11) shows about $4.3m a year on a lease average of about five years</t>
         </is>
       </c>
       <c r="D1907" s="7" t="inlineStr">
@@ -47509,7 +47509,7 @@
       </c>
       <c r="E1907" s="7" t="inlineStr">
         <is>
-          <t>Amount matters less than timing: paid as the leases run, the covenant is clear and minimum liquidity is about $1m below ABC Private Credit's figure; paid inside four quarters, for example to buy out the leases, it is about $17m lower and below the covenant</t>
+          <t>Amount matters less than timing: paid as the leases run, the covenant is clear and minimum liquidity is about $1m below Alder Point Credit's figure; paid inside four quarters, for example to buy out the leases, it is about $17m lower and below the covenant</t>
         </is>
       </c>
     </row>
@@ -47548,7 +47548,7 @@
       </c>
       <c r="B1909" s="7" t="inlineStr">
         <is>
-          <t>Liquidity covenant first breached at 6.6% (9.0% on ABC Private Credit's closure figure; 2.0% if the loan is drawn only when cash is short); leverage covenant at 46%; at 9% with no closure benefit liquidity is below $21.5m from the December 2027 quarter</t>
+          <t>Liquidity covenant first breached at 6.6% (9.0% on Alder Point Credit's closure figure; 2.0% if the loan is drawn only when cash is short); leverage covenant at 46%; at 9% with no closure benefit liquidity is below $21.5m from the December 2027 quarter</t>
         </is>
       </c>
       <c r="C1909" s="7" t="inlineStr">
@@ -47680,7 +47680,7 @@
       </c>
       <c r="D1917" s="7" t="inlineStr">
         <is>
-          <t>Rent treatment decides what the ratio measures [I]. Without rent in the denominator the ratio is 6.28x at close against 6.35x; in our illustrative cases the ABC Private Credit model v24 case would then sit above the level at the first test and the DDTL could not be drawn [I]. The EBITDAR (lease-consistent) reading is also the construction ABC Private Credit's model v24 uses (MODEL OUTPUT rows 52–46: 4.46x at the first quarterly test) [A]. The stock-compensation add-back loosens the covenant further and, in our illustrative downside, moves the Liquidity shortfall by two quarters [I].</t>
+          <t>Rent treatment decides what the ratio measures [I]. Without rent in the denominator the ratio is 6.28x at close against 6.35x; in our illustrative cases the Alder Point Credit model v24 case would then sit above the level at the first test and the DDTL could not be drawn [I]. The EBITDAR (lease-consistent) reading is also the construction Alder Point Credit's model v24 uses (MODEL OUTPUT rows 52–46: 4.46x at the first quarterly test) [A]. The stock-compensation add-back loosens the covenant further and, in our illustrative downside, moves the Liquidity shortfall by two quarters [I].</t>
         </is>
       </c>
     </row>
@@ -47695,12 +47695,12 @@
       </c>
       <c r="C1918" s="7" t="inlineStr">
         <is>
-          <t>The 6.35x–5.81x schedule sits well above the paths in our illustrative cases, in ABC Private Credit's model v24 and in CreditSwan's monthly lead case on that model, set out under 08 B earlier in this section (peak 4.53x, note C-FIN-1); on these levels the leverage covenant gives no earlier warning than Liquidity in any of our illustrative downside cases.</t>
+          <t>The 6.35x–5.81x schedule sits well above the paths in our illustrative cases, in Alder Point Credit's model v24 and in CreditSwan's monthly lead case on that model, set out under 08 B earlier in this section (peak 4.53x, note C-FIN-1); on these levels the leverage covenant gives no earlier warning than Liquidity in any of our illustrative downside cases.</t>
         </is>
       </c>
       <c r="D1918" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model v24 path sits 27–35% below 6.35x–5.81x on an EBITDAR basis, and our illustrative base case would need a 42% EBITDA shortfall to reach the level [A/I]; Deal A's own annual EBITDA declines have been 11.9%, 6.7%, 23.5% and 19.9% on audited E1 (FY23–FY26), 33.2% on E1 excluding disposal gains in FY26, and 34% year on year in Q1 FY27 on company non-GAAP EBITDA (E2m, PF) [F/I].</t>
+          <t>Alder Point Credit's model v24 path sits 27–35% below 6.35x–5.81x on an EBITDAR basis, and our illustrative base case would need a 42% EBITDA shortfall to reach the level [A/I]; Deal A's own annual EBITDA declines have been 11.9%, 6.7%, 23.5% and 19.9% on audited E1 (FY23–FY26), 33.2% on E1 excluding disposal gains in FY26, and 34% year on year in Q1 FY27 on company non-GAAP EBITDA (E2m, PF) [F/I].</t>
         </is>
       </c>
     </row>
@@ -47715,12 +47715,12 @@
       </c>
       <c r="C1919" s="7" t="inlineStr">
         <is>
-          <t>As written, the DDTL condition appears to be tested at each draw, pro forma, on trailing EBITDA; the use of proceeds covers payments due within 107 days of each draw. It would help us to understand which reading ABC Private Credit intends.</t>
+          <t>As written, the DDTL condition appears to be tested at each draw, pro forma, on trailing EBITDA; the use of proceeds covers payments due within 107 days of each draw. It would help us to understand which reading Alder Point Credit intends.</t>
         </is>
       </c>
       <c r="D1919" s="7" t="inlineStr">
         <is>
-          <t>The SCF balance to be unwound is $140m, $177m or $184m depending on scope [I], and $122.6m of the SCF aging is already over 107 days, against the term sheet's 107-day eligibility language [F, SCF aging]. Testing each draw on trailing EBITDA can block funding without reducing leverage, because the draw replaces a payable [I]. In our illustrative base case (the quarterly model) the March 2027 draw passes at 4.76x (a 3.0% cushion), and in the monthly lead case on ABC Private Credit's model v24 at 4.60x (a 4.7% cushion) [I, C-FIN-1]; a one-quarter COVID-type shock at the start of the unwind exhausts base-case cash as written, but not when the test is applied once at close. At 5.15x our illustrative downside passes a once-at-close test by only 0.010x [I].</t>
+          <t>The SCF balance to be unwound is $140m, $177m or $184m depending on scope [I], and $122.6m of the SCF aging is already over 107 days, against the term sheet's 107-day eligibility language [F, SCF aging]. Testing each draw on trailing EBITDA can block funding without reducing leverage, because the draw replaces a payable [I]. In our illustrative base case (the quarterly model) the March 2027 draw passes at 4.76x (a 3.0% cushion), and in the monthly lead case on Alder Point Credit's model v24 at 4.60x (a 4.7% cushion) [I, C-FIN-1]; a one-quarter COVID-type shock at the start of the unwind exhausts base-case cash as written, but not when the test is applied once at close. At 5.15x our illustrative downside passes a once-at-close test by only 0.010x [I].</t>
         </is>
       </c>
     </row>
@@ -47740,7 +47740,7 @@
       </c>
       <c r="D1920" s="7" t="inlineStr">
         <is>
-          <t>While the $67m cap applies, with $44m drawn and $25.5m of letters of credit, availability is exactly $21.5m, the covenant minimum [I]. In our illustrative quarterly cases, which do not charge finance-lease interest, the ABC Private Credit model v24 case drawn as ABC Private Credit's model draws it ($86m, cap kept on) averages $13.2m of daily Liquidity in the September 2027 quarter, and $50m with $111m drawn [I]; in the monthly lead case on ABC Private Credit's model v24 (Exhibit 9.157) the full $111m is drawn by April 2027, the cap lifts and the September 2027 quarter averages $55.5m [I, C-FIN-1]. In our illustrative case on the 10-Q's SCF scope, without the build-up on the Lender 6 line and with a weak September quarter, Liquidity bottoms at $8.0m if the cap lifts when a draw is partly refused, and cash runs out in the September 2027 quarter if it does not [I].</t>
+          <t>While the $67m cap applies, with $44m drawn and $25.5m of letters of credit, availability is exactly $21.5m, the covenant minimum [I]. In our illustrative quarterly cases, which do not charge finance-lease interest, the Alder Point Credit model v24 case drawn as Alder Point Credit's model draws it ($86m, cap kept on) averages $13.2m of daily Liquidity in the September 2027 quarter, and $50m with $111m drawn [I]; in the monthly lead case on Alder Point Credit's model v24 (Exhibit 9.157) the full $111m is drawn by April 2027, the cap lifts and the September 2027 quarter averages $55.5m [I, C-FIN-1]. In our illustrative case on the 10-Q's SCF scope, without the build-up on the Lender 6 line and with a weak September quarter, Liquidity bottoms at $8.0m if the cap lifts when a draw is partly refused, and cash runs out in the September 2027 quarter if it does not [I].</t>
         </is>
       </c>
     </row>
@@ -47800,7 +47800,7 @@
       </c>
       <c r="D1923" s="7" t="inlineStr">
         <is>
-          <t>The December 2026 payment falls two quarters before our illustrative downside's Liquidity shortfall, and not paying it is what keeps our illustrative SCF-squeeze case above $21m ($25.5m against $18.4m); a fully used G&amp;A bucket releases dividends that take the management case below $21m [I]. The $12m run-rate second-round benefit [M, CIP p.1] is before up to $2.1–4.7m a year of stranded corporate overhead (an upper bound that assumes all of the overhead attributable to the 119 clinics stays behind) and $1.1–1.9m of stranded advertising (at Deal A's own 1.38% (FY25) to 2.36% (FY26) advertising-to-sales ratio on the 119 clinics' sales, Part 05 section D), and $3.4–4.3m of it rests on a 13% sales-recapture assumption that no peer has measured [I]. ABC Private Credit's model v24 FCCR of 1.23x at close excludes finance-lease interest; including it gives about 0.93x, below the 1.03x dividend gate [A/I].</t>
+          <t>The December 2026 payment falls two quarters before our illustrative downside's Liquidity shortfall, and not paying it is what keeps our illustrative SCF-squeeze case above $21m ($25.5m against $18.4m); a fully used G&amp;A bucket releases dividends that take the management case below $21m [I]. The $12m run-rate second-round benefit [M, CIP p.1] is before up to $2.1–4.7m a year of stranded corporate overhead (an upper bound that assumes all of the overhead attributable to the 119 clinics stays behind) and $1.1–1.9m of stranded advertising (at Deal A's own 1.38% (FY25) to 2.36% (FY26) advertising-to-sales ratio on the 119 clinics' sales, Part 05 section D), and $3.4–4.3m of it rests on a 13% sales-recapture assumption that no peer has measured [I]. Alder Point Credit's model v24 FCCR of 1.23x at close excludes finance-lease interest; including it gives about 0.93x, below the 1.03x dividend gate [A/I].</t>
         </is>
       </c>
     </row>
@@ -47915,12 +47915,12 @@
       </c>
       <c r="C1929" s="7" t="inlineStr">
         <is>
-          <t>The term sheet states the term loan's amortisation and gives the delayed-draw loans identical terms, without a separate DDTL amortisation schedule (our illustrative cases assume the term loan's 1%). ABC Private Credit's model v24 row 43 keeps the DDTL at cumulative draws and does not reflect the amortisation paid in row 31, and its cell I108 points to N36 rather than R36; separately, the finance-lease interest component is not charged to cash (MODEL OUTPUT!D30 and D171).</t>
+          <t>The term sheet states the term loan's amortisation and gives the delayed-draw loans identical terms, without a separate DDTL amortisation schedule (our illustrative cases assume the term loan's 1%). Alder Point Credit's model v24 row 43 keeps the DDTL at cumulative draws and does not reflect the amortisation paid in row 31, and its cell I108 points to N36 rather than R36; separately, the finance-lease interest component is not charged to cash (MODEL OUTPUT!D30 and D171).</t>
         </is>
       </c>
       <c r="D1929" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model v24 overstates debt by $0.5–0.8m [I]. The finance-lease interest not charged to cash is $2.0m in Q3 FY27 and $28.4m cumulatively through FY31 [F, ABC Private Credit Deal A Model v24 MODEL OUTPUT!D30 =+D171-D22, D171].</t>
+          <t>Alder Point Credit's model v24 overstates debt by $0.5–0.8m [I]. The finance-lease interest not charged to cash is $2.0m in Q3 FY27 and $28.4m cumulatively through FY31 [F, Alder Point Credit Deal A Model v24 MODEL OUTPUT!D30 =+D171-D22, D171].</t>
         </is>
       </c>
     </row>
@@ -47940,7 +47940,7 @@
       </c>
       <c r="D1930" s="7" t="inlineStr">
         <is>
-          <t>On the 10-Q's SCF scope our illustrative base case falls below its Liquidity covenant at every unwind speed except a late run-off [I]. Recovery is a real-estate question: NOLV of $228m covers funded debt 1.27x at close only with the $152m of owned real estate (the company's estimate of fair market value, built on tax-assessed values; no third-party appraisal) [F/M, Diligence &amp; Structure Update p.36; ABC Private Credit Diligence Tracker, tab ABC Private Credit, J59]; without it NOLV is $76m — 0.43x at close and 0.24x at our illustrative base-case peak [I] — and at the maximum funded amount of $284m the facilities exceed NOLV by $58m (total commitments of $336m exceed it by $101.6m) [I].</t>
+          <t>On the 10-Q's SCF scope our illustrative base case falls below its Liquidity covenant at every unwind speed except a late run-off [I]. Recovery is a real-estate question: NOLV of $228m covers funded debt 1.27x at close only with the $152m of owned real estate (the company's estimate of fair market value, built on tax-assessed values; no third-party appraisal) [F/M, Diligence &amp; Structure Update p.36; Alder Point Credit Diligence Tracker, tab Alder Point Credit, J59]; without it NOLV is $76m — 0.43x at close and 0.24x at our illustrative base-case peak [I] — and at the maximum funded amount of $284m the facilities exceed NOLV by $58m (total commitments of $336m exceed it by $101.6m) [I].</t>
         </is>
       </c>
     </row>
@@ -47967,7 +47967,7 @@
     <row r="1932" ht="39" customHeight="1">
       <c r="A1932" s="9" t="inlineStr">
         <is>
-          <t>Source: DLA-023 (LW draft term sheet (21 September 2026)); ABC Private Credit Deal A Model v24; Deal A FY26 10-K and Q1 FY27 10-Q; Diligence &amp; Structure Update; Alpha - FY27 Clinic Closure Data; CreditSwan illustrative cases (quarterly model of the proposed facilities; notes C-FIN-6 and C-FIN-7) · Basis: Illustrative cases P; they take the finance-lease cash line as ABC Private Credit's model has it and do not charge its interest component; tags as marked in each cell</t>
+          <t>Source: DLA-023 (LW draft term sheet (21 September 2026)); Alder Point Credit Deal A Model v24; Deal A FY26 10-K and Q1 FY27 10-Q; Diligence &amp; Structure Update; Alpha - FY27 Clinic Closure Data; CreditSwan illustrative cases (quarterly model of the proposed facilities; notes C-FIN-6 and C-FIN-7) · Basis: Illustrative cases P; they take the finance-lease cash line as Alder Point Credit's model has it and do not charge its interest component; tags as marked in each cell</t>
         </is>
       </c>
     </row>
@@ -48394,7 +48394,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>The answer, the three theses side by side, what ABC Private Credit asked, the sector in brief, what holds across the deals, the evidence base, and what carries forward</t>
+          <t>The answer, the three theses side by side, what Alder Point Credit asked, the sector in brief, what holds across the deals, the evidence base, and what carries forward</t>
         </is>
       </c>
     </row>
@@ -48406,7 +48406,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's six industry questions, (i) to (vi), one section each</t>
+          <t>Alder Point Credit's six industry questions, (i) to (vi), one section each</t>
         </is>
       </c>
     </row>
@@ -48466,7 +48466,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>The proposed financings of the three deals, as observations for ABC Private Credit's own underwriting</t>
+          <t>The proposed financings of the three deals, as observations for Alder Point Credit's own underwriting</t>
         </is>
       </c>
     </row>
@@ -48716,7 +48716,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>The weak clinics are an identifiable group: 104 of the 119 second-round clinics sit in ABC Private Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4% and the clinic margin on ABC Private Credit's basis from 12.8% to 14.4% (FY26) (Part 05 section B, Part 05 section E)</t>
+          <t>The weak clinics are an identifiable group: 104 of the 119 second-round clinics sit in Alder Point Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4% and the clinic margin on Alder Point Credit's basis from 12.8% to 14.4% (FY26) (Part 05 section B, Part 05 section E)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -48807,12 +48807,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Partially supported (leans supported) — on ABC Private Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three</t>
+          <t>Partially supported (leans supported) — on Alder Point Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Scale: 983 clinics and $1,029.1m of FY26 revenue; on ABC Private Credit's basis after finance-lease cost the 824 clinics kept earn 12.5%, in the lower half of the 10.7–17.4% peer band (indicative); the ticket kept pace with veterinary prices in FY26 (Part 05 section E; Part 09 section L)</t>
+          <t>Scale: 983 clinics and $1,029.1m of FY26 revenue; on Alder Point Credit's basis after finance-lease cost the 824 clinics kept earn 12.5%, in the lower half of the 10.7–17.4% peer band (indicative); the ticket kept pace with veterinary prices in FY26 (Part 05 section E; Part 09 section L)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -49009,7 +49009,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Four-wall EBITDA of $5.42m in January–July 2026, 25.9% below the seller's same months; visit count −11.9% in the first quarter (−11.5% a day), −16.1% in the second and −17.3% a day in July; the company's recovery to −15.6% in September rests on weekly data not in the files; a value of $33–46m on wellness clinic multiples reaches ABC Private Credit's $44m only at its top (Part 06 section F)</t>
+          <t>Four-wall EBITDA of $5.42m in January–July 2026, 25.9% below the seller's same months; visit count −11.9% in the first quarter (−11.5% a day), −16.1% in the second and −17.3% a day in July; the company's recovery to −15.6% in September rests on weekly data not in the files; a value of $33–46m on wellness clinic multiples reaches Alder Point Credit's $44m only at its top (Part 06 section F)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -49137,7 +49137,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>$9.2m of ABC Private Credit's $29.4m (LTM September 2026E, P) is pre-acquisition and letter-of-intent earnings; cash EBITDA 0.28–0.31 of pro forma against a 0.73 peer median (Part 07 section D, Part 07 section F)</t>
+          <t>$9.2m of Alder Point Credit's $29.4m (LTM September 2026E, P) is pre-acquisition and letter-of-intent earnings; cash EBITDA 0.28–0.31 of pro forma against a 0.73 peer median (Part 07 section D, Part 07 section F)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -49188,14 +49188,14 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 1.06 — At October 2026 each of ABC Private Credit's thirteen asks has an answer here; the industry questions and the benchmark rest on up to eleven benchmark operators (thirteen for same-store sales), and the three theses hold in part</t>
+          <t>Exhibit 1.06 — At October 2026 each of Alder Point Credit's thirteen asks has an answer here; the industry questions and the benchmark rest on up to eleven benchmark operators (thirteen for same-store sales), and the three theses hold in part</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>ABC Private Credit's goals for the study, in ABC Private Credit's words (September 2026), our answer in one line, and where it is substantiated</t>
+          <t>Alder Point Credit's goals for the study, in Alder Point Credit's words (September 2026), our answer in one line, and where it is substantiated</t>
         </is>
       </c>
     </row>
@@ -49207,7 +49207,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>What ABC Private Credit asked</t>
+          <t>What Alder Point Credit asked</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -49454,7 +49454,7 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>The weakest clinics are an identifiable tail, and closing them lifts clinic margin; on ABC Private Credit's basis after finance-lease cost the clinics kept sit in the lower half of the peer band; traffic is falling across the clinics kept; the second round's value turns on how the company measures clinic contribution; the financing is read in Part 08 section B</t>
+          <t>The weakest clinics are an identifiable tail, and closing them lifts clinic margin; on Alder Point Credit's basis after finance-lease cost the clinics kept sit in the lower half of the peer band; traffic is falling across the clinics kept; the second round's value turns on how the company measures clinic contribution; the financing is read in Part 08 section B</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -49510,7 +49510,7 @@
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Source: ABC Private Credit's note "Pet Care Services Project" (goals G1 to G13); the answers are summarised from the supplies named in the last column, where their sources are given · Basis: Summary of the supplies named; readings are our reading on the evidence supplied to date · Assumption: A-01, A-02, A-03, A-10</t>
+          <t>Source: Alder Point Credit's note "Pet Care Services Project" (goals G1 to G13); the answers are summarised from the supplies named in the last column, where their sources are given · Basis: Summary of the supplies named; readings are our reading on the evidence supplied to date · Assumption: A-01, A-02, A-03, A-10</t>
         </is>
       </c>
     </row>
@@ -49524,7 +49524,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Our answer on each of the eight areas ABC Private Credit asked about, what is durable, temporary or company-specific, and how deep the evidence is; operator records from FY1996 to 2026</t>
+          <t>Our answer on each of the eight areas Alder Point Credit asked about, what is durable, temporary or company-specific, and how deep the evidence is; operator records from FY1996 to 2026</t>
         </is>
       </c>
     </row>
@@ -49863,7 +49863,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>On ABC Private Credit's basis, co-op included and finance-lease cost at book, 10.7% (FY26) and 12.5% for the clinics kept (pro forma): at the floor of the 10.7–17.4% peer range and in its lower half, indicatively; 5.4–7.9% before co-op, on a rent treatment no peer shares (Exhibit 1.12)</t>
+          <t>On Alder Point Credit's basis, co-op included and finance-lease cost at book, 10.7% (FY26) and 12.5% for the clinics kept (pro forma): at the floor of the 10.7–17.4% peer range and in its lower half, indicatively; 5.4–7.9% before co-op, on a rent treatment no peer shares (Exhibit 1.12)</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -49878,7 +49878,7 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Does not transfer: each deal has a different set of valid comparators (Part 04 section F); Deal A's placement on ABC Private Credit's basis is indicative, as its co-op is allocated at a flat rate and its rent is at book</t>
+          <t>Does not transfer: each deal has a different set of valid comparators (Part 04 section F); Deal A's placement on Alder Point Credit's basis is indicative, as its co-op is allocated at a flat rate and its rent is at book</t>
         </is>
       </c>
     </row>
@@ -50754,7 +50754,7 @@
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>The share falling below the 27–32% it has held in FY23 to FY26 before co-op, or below 19.5% (FY26) on ABC Private Credit's basis with co-op allocated to clinics (11.4% for the clinics kept after the second round)</t>
+          <t>The share falling below the 27–32% it has held in FY23 to FY26 before co-op, or below 19.5% (FY26) on Alder Point Credit's basis with co-op allocated to clinics (11.4% for the clinics kept after the second round)</t>
         </is>
       </c>
     </row>
@@ -50798,7 +50798,7 @@
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Set out in Part 08, for ABC Private Credit's own underwriting</t>
+          <t>Set out in Part 08, for Alder Point Credit's own underwriting</t>
         </is>
       </c>
     </row>
@@ -51105,21 +51105,21 @@
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 3.01 — On the six measures ABC Private Credit asked about, volume has been flat and, outside 2020, steady, the ticket has carried growth and clinic margins before rebates moved within 1.3–5.4 points at each operator (FY08 to 2026); rebates, overhead and recurring acquisition costs make platform earnings and cash less steady</t>
+          <t>Exhibit 3.01 — On the six measures Alder Point Credit asked about, volume has been flat and, outside 2020, steady, the ticket has carried growth and clinic margins before rebates moved within 1.3–5.4 points at each operator (FY08 to 2026); rebates, overhead and recurring acquisition costs make platform earnings and cash less steady</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Our answer on each of ABC Private Credit's six industry questions, (i) to (vi), with the depth of the evidence and what would change it; operator records from FY1996 to 2026</t>
+          <t>Our answer on each of Alder Point Credit's six industry questions, (i) to (vi), with the depth of the evidence and what would change it; operator records from FY1996 to 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Alder Point Credit asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -51977,7 +51977,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>SSS_CD CLOSE-FWD; SSS_CO-PF 2018 and SSS_ST-59 ABC Private Credit 2023–25 (CLOSE-UNK)</t>
+          <t>SSS_CD CLOSE-FWD; SSS_CO-PF 2018 and SSS_ST-59 Alder Point Credit 2023–25 (CLOSE-UNK)</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -53102,14 +53102,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Our answer on each of ABC Private Credit's asks on multiples, leverage, the benchmark, the scope of wellness clinics and emergency and specialty hospitals, and what public sources add; transactions 2012–26, operator records to 2026 (the longest from FY1996, Deal A), public sources read on 30 September 2026 (census income 2020–2024)</t>
+          <t>Our answer on each of Alder Point Credit's asks on multiples, leverage, the benchmark, the scope of wellness clinics and emergency and specialty hospitals, and what public sources add; transactions 2012–26, operator records to 2026 (the longest from FY1996, Deal A), public sources read on 30 September 2026 (census income 2020–2024)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Alder Point Credit asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -53536,7 +53536,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Leverage at close (x) on financing EBITDA by rung and market environment: count, minimum, median and maximum of closed prints, proposals shown apart, 2014 to 2026; ABC Private Credit deal documents</t>
+          <t>Leverage at close (x) on financing EBITDA by rung and market environment: count, minimum, median and maximum of closed prints, proposals shown apart, 2014 to 2026; Alder Point Credit deal documents</t>
         </is>
       </c>
     </row>
@@ -55058,7 +55058,7 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Deal A's audited record, the longest in the files, shows a large general practice and pharmacy estate whose visits, clinic profit and reported margin fell together in the 2024 to 2026 soft period, with a third of clinics losing money in every year from FY23 to FY26 before co-op (19.5% in FY26 with co-op allocated to clinics, ABC Private Credit's basis).</t>
+          <t>Deal A's audited record, the longest in the files, shows a large general practice and pharmacy estate whose visits, clinic profit and reported margin fell together in the 2024 to 2026 soft period, with a third of clinics losing money in every year from FY23 to FY26 before co-op (19.5% in FY26 with co-op allocated to clinics, Alder Point Credit's basis).</t>
         </is>
       </c>
     </row>
@@ -55099,7 +55099,7 @@
     <row r="85" ht="39" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>Source: The eleven operator profiles in Part 09 section K, where each figure carries its references; Deal A's loss-making share on ABC Private Credit's basis from Part 05 section E · Basis: Each operator on its own best available data, period, rent code and clinic base; described, not ranked (Part 04 section E); live-deal profiles carry operating measures only · Assumption: A-01, A-02, A-07</t>
+          <t>Source: The eleven operator profiles in Part 09 section K, where each figure carries its references; Deal A's loss-making share on Alder Point Credit's basis from Part 05 section E · Basis: Each operator on its own best available data, period, rent code and clinic base; described, not ranked (Part 04 section E); live-deal profiles carry operating measures only · Assumption: A-01, A-02, A-07</t>
         </is>
       </c>
     </row>
@@ -56283,7 +56283,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>In this part the comparison departs from this: for Deal A, clinic margins are shown on ABC Private Credit's co-op-included basis and before co-op, with finance-lease cost labelled between them, and peers co-op-included on cash rent; each treatment is named and never pooled</t>
+          <t>In this part the comparison departs from this: for Deal A, clinic margins are shown on Alder Point Credit's co-op-included basis and before co-op, with finance-lease cost labelled between them, and peers co-op-included on cash rent; each treatment is named and never pooled</t>
         </is>
       </c>
     </row>
@@ -56334,7 +56334,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>$21.79m spread evenly over 42.1 months from April 2027, plus $4.3m of professional fees in ABC Private Credit's model in April to June 2027</t>
+          <t>$21.79m spread evenly over 42.1 months from April 2027, plus $4.3m of professional fees in Alder Point Credit's model in April to June 2027</t>
         </is>
       </c>
     </row>
@@ -56358,21 +56358,21 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 5.01 — Three of Deal A's four business components read partially supported, two of them leaning supported on ABC Private Credit's rebates-included basis; the second round's value turns on a definition Deal A has not yet given (evidence to October 2026)</t>
+          <t>Exhibit 5.01 — Three of Deal A's four business components read partially supported, two of them leaning supported on Alder Point Credit's rebates-included basis; the second round's value turns on a definition Deal A has not yet given (evidence to October 2026)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Our reading on each component of ABC Private Credit's Deal A thesis (M1 to M5), with the depth of the evidence and what would change it; FY20 to the first quarter of FY27, files to 1 October 2026</t>
+          <t>Our reading on each component of Alder Point Credit's Deal A thesis (M1 to M5), with the depth of the evidence and what would change it; FY20 to the first quarter of FY27, files to 1 October 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Alder Point Credit asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -56399,12 +56399,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Partially supported (leans supported) — the tail is identifiable and closing it lifts clinic margin; the decline across retained clinics is not addressed by closures. 104 of the 119 second-round clinics sit in ABC Private Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4%; with quartiles fixed at FY23, the top half's clinic EBITDA fell 16% to FY26 (Part 05 section B, Part 05 section E).</t>
+          <t>Partially supported (leans supported) — the tail is identifiable and closing it lifts clinic margin; the decline across retained clinics is not addressed by closures. 104 of the 119 second-round clinics sit in Alder Point Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4%; with quartiles fixed at FY23, the top half's clinic EBITDA fell 16% to FY26 (Part 05 section B, Part 05 section E).</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Deal A's clinic-level earnings files FY23–FY26 and KPI files to the first quarter of FY27 (actual); the 119-clinic list of 1 October; co-op allocated at ABC Private Credit's rate; ABC Private Credit's quartile view reproduced exactly.</t>
+          <t>Deal A's clinic-level earnings files FY23–FY26 and KPI files to the first quarter of FY27 (actual); the 119-clinic list of 1 October; co-op allocated at Alder Point Credit's rate; Alder Point Credit's quartile view reproduced exactly.</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -56448,7 +56448,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>The 119-clinic list (clinic results, rent, lease terms and cost to close, LTM June 2026); company estimates; ABC Private Credit's model; overhead ratios of three platforms, pro forma for two. No lease-exit plan.</t>
+          <t>The 119-clinic list (clinic results, rent, lease terms and cost to close, LTM June 2026); company estimates; Alder Point Credit's model; overhead ratios of three platforms, pro forma for two. No lease-exit plan.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -56465,7 +56465,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Partially supported (leans supported) — on ABC Private Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three. On ABC Private Credit's basis the clinic margin is 12.8% for all clinics and 14.4% for the 824 kept; after finance-lease cost, 10.7% and 12.5% against a 10.7–17.4% peer band (indicative); comparable traffic at the clinics kept −3.2% in FY26 against −2.0% to −2.8% (Part 05 section E).</t>
+          <t>Partially supported (leans supported) — on Alder Point Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three. On Alder Point Credit's basis the clinic margin is 12.8% for all clinics and 14.4% for the 824 kept; after finance-lease cost, 10.7% and 12.5% against a 10.7–17.4% peer band (indicative); comparable traffic at the clinics kept −3.2% in FY26 against −2.0% to −2.8% (Part 05 section E).</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -56504,21 +56504,21 @@
     <row r="20" ht="39" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Source: Part 05 section A to Part 05 section G, and Part 08 section B for M5 · Basis: Mostly actual (A); clinic margins on ABC Private Credit's basis allocate co-op at a flat rate [I]; the second-round cases are pro forma run rates (PF) on the company's clinic measures; financing on the recapitalisation model of 29 September (P)</t>
+          <t>Source: Part 05 section A to Part 05 section G, and Part 08 section B for M5 · Basis: Mostly actual (A); clinic margins on Alder Point Credit's basis allocate co-op at a flat rate [I]; the second-round cases are pro forma run rates (PF) on the company's clinic measures; financing on the recapitalisation model of 29 September (P)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 5.02 — Deal A's weakest clinics are an identifiable tail and closing them lifts clinic margin, on ABC Private Credit's basis after finance-lease cost, to the lower half of the peer band; traffic is falling across the clinics it keeps and the second round's value turns on how the company measures clinic contribution (evidence to October 2026)</t>
+          <t>Exhibit 5.02 — Deal A's weakest clinics are an identifiable tail and closing them lifts clinic margin, on Alder Point Credit's basis after finance-lease cost, to the lower half of the peer band; traffic is falling across the clinics it keeps and the second round's value turns on how the company measures clinic contribution (evidence to October 2026)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>ABC Private Credit's thesis on Deal A by component: our reading on the evidence supplied to date, its basis, what holds, what does not and what would change it; FY23 to Q1 FY27, files to 1 October 2026</t>
+          <t>Alder Point Credit's thesis on Deal A by component: our reading on the evidence supplied to date, its basis, what holds, what does not and what would change it; FY23 to Q1 FY27, files to 1 October 2026</t>
         </is>
       </c>
     </row>
@@ -56567,12 +56567,12 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's quartile view reproduced exactly from the clinic files; 104 of the 119 second-round clinics in its bottom quartile; loss-making share including co-op 19.5% for all clinics, 11.4% for the 824 kept; quartiles fixed at FY23 for the same clinics (clinic-level EBITDA file; Data Cuts; FY27 Closing Clinics Financial Analysis)</t>
+          <t>Alder Point Credit's quartile view reproduced exactly from the clinic files; 104 of the 119 second-round clinics in its bottom quartile; loss-making share including co-op 19.5% for all clinics, 11.4% for the 824 kept; quartiles fixed at FY23 for the same clinics (clinic-level EBITDA file; Data Cuts; FY27 Closing Clinics Financial Analysis)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>The weak clinics are an identifiable group: 104 of the 119 second-round clinics sit in ABC Private Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4% and the clinic margin on ABC Private Credit's basis from 12.8% to 14.4% (FY26); rank is sticky (Part 05 section B, Part 05 section E)</t>
+          <t>The weak clinics are an identifiable group: 104 of the 119 second-round clinics sit in Alder Point Credit's bottom quartile, and closing them takes the loss-making share including co-op from 19.5% to 11.4% and the clinic margin on Alder Point Credit's basis from 12.8% to 14.4% (FY26); rank is sticky (Part 05 section B, Part 05 section E)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -56658,7 +56658,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Partially supported (leans supported) — on ABC Private Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three</t>
+          <t>Partially supported (leans supported) — on Alder Point Credit's basis after finance-lease cost, the clinics kept sit in the lower half of the peer band; traffic remains last of three</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -56668,7 +56668,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Scale: 983 clinics and $1,029.1m of FY26 revenue; on ABC Private Credit's basis after finance-lease cost the 824 clinics kept earn 12.5%, in the lower half of the 10.7–17.4% peer band (indicative); the ticket kept pace with veterinary prices in FY26 (Part 05 section E; Part 09 section L)</t>
+          <t>Scale: 983 clinics and $1,029.1m of FY26 revenue; on Alder Point Credit's basis after finance-lease cost the 824 clinics kept earn 12.5%, in the lower half of the 10.7–17.4% peer band (indicative); the ticket kept pace with veterinary prices in FY26 (Part 05 section E; Part 09 section L)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -56717,21 +56717,21 @@
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Source: Deal A clinic-level EBITDA file FY23–FY26; New Deal A Data Cuts (Aug-26); FY27 Closing Clinics Financial Analysis (DLA-027); ABC Private Credit's Diligence &amp; Structure Update p.9; Project Alpha CIP p.1; Deal A FY26 10-K; Project Alpha Recapitalization Model v06 (DLA-026); each item as cited in the section named · Basis: A (filings, clinic files); clinic margins on ABC Private Credit's basis allocate co-op at a flat rate [I]; second-round cases pro forma (PF) on company clinic measures [F/I]; management plan (P); recapitalisation model (P) · Assumption: A-01, A-02, A-07, A-F2, A-P7</t>
+          <t>Source: Deal A clinic-level EBITDA file FY23–FY26; New Deal A Data Cuts (Aug-26); FY27 Closing Clinics Financial Analysis (DLA-027); Alder Point Credit's Diligence &amp; Structure Update p.9; Project Alpha CIP p.1; Deal A FY26 10-K; Project Alpha Recapitalization Model v06 (DLA-026); each item as cited in the section named · Basis: A (filings, clinic files); clinic margins on Alder Point Credit's basis allocate co-op at a flat rate [I]; second-round cases pro forma (PF) on company clinic measures [F/I]; management plan (P); recapitalisation model (P) · Assumption: A-01, A-02, A-07, A-F2, A-P7</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 5.10 — Spread over the 42.1-month average lease term, the workbook's $21.79m of closure cash is about $5.36m a year in FY28–FY31, against $4.3m in FY28 alone in ABC Private Credit's model</t>
+          <t>Exhibit 5.10 — Spread over the 42.1-month average lease term, the workbook's $21.79m of closure cash is about $5.36m a year in FY28–FY31, against $4.3m in FY28 alone in Alder Point Credit's model</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Second-round closure cost for 119 clinics by component and by fiscal year, $m: company workbook against ABC Private Credit model v24</t>
+          <t>Second-round closure cost for 119 clinics by component and by fiscal year, $m: company workbook against Alder Point Credit model v24</t>
         </is>
       </c>
     </row>
@@ -56748,7 +56748,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model</t>
+          <t>Alder Point Credit's model</t>
         </is>
       </c>
     </row>
@@ -56950,7 +56950,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model: closure cash</t>
+          <t>Alder Point Credit's model: closure cash</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
@@ -56975,7 +56975,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model: professional fees</t>
+          <t>Alder Point Credit's model: professional fees</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
@@ -57000,7 +57000,7 @@
     <row r="51" ht="52" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Source: Alpha - FY27 Clinic Closure Data, Summary!J32, J33, J37:J47, B49; ABC Private Credit Deal A Model v24, MODEL OUTPUT!F20:I20, F21; Diligence &amp; Structure Update p.11; timing by fiscal year: C-FIN-4 · Basis: M (company estimate, a maximum before lease assignments); A (ABC Private Credit model). Timing [I] · Assumption: The workbook gives no clinic-by-clinic schedule; its cash is spread evenly over the average remaining term of 42.1 months from April 2027, the month ABC Private Credit's model starts the closure. Deferred maintenance and the owned clinics' six-month costs would fall earlier</t>
+          <t>Source: Alpha - FY27 Clinic Closure Data, Summary!J32, J33, J37:J47, B49; Alder Point Credit Deal A Model v24, MODEL OUTPUT!F20:I20, F21; Diligence &amp; Structure Update p.11; timing by fiscal year: C-FIN-4 · Basis: M (company estimate, a maximum before lease assignments); A (Alder Point Credit model). Timing [I] · Assumption: The workbook gives no clinic-by-clinic schedule; its cash is spread evenly over the average remaining term of 42.1 months from April 2027, the month Alder Point Credit's model starts the closure. Deferred maintenance and the owned clinics' six-month costs would fall earlier</t>
         </is>
       </c>
     </row>
@@ -57107,7 +57107,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit $4.3m of cash in FY28 plus $4.3m of fees</t>
+          <t>Alder Point Credit $4.3m of cash in FY28 plus $4.3m of fees</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -57122,7 +57122,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model differs in amount and in timing: the workbook (and ABC Private Credit's Diligence &amp; Structure Update, up to $21.5m) spreads the cash over the lease terms, about $5.3m a year from FY28 to FY31, against $4.3m in FY28 alone in ABC Private Credit's model; its effect on liquidity is in Part 08 section E; dark rent is the larger exposure in the one peer programme on file</t>
+          <t>Alder Point Credit's model differs in amount and in timing: the workbook (and Alder Point Credit's Diligence &amp; Structure Update, up to $21.5m) spreads the cash over the lease terms, about $5.3m a year from FY28 to FY31, against $4.3m in FY28 alone in Alder Point Credit's model; its effect on liquidity is in Part 08 section E; dark rent is the larger exposure in the one peer programme on file</t>
         </is>
       </c>
     </row>
@@ -57183,7 +57183,7 @@
     <row r="61" ht="39" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>Source: Observed ranges of Part 03 and Part 04 with the fact rows and exhibits in each cell; Alpha - FY27 Clinic Closure Data, Summary!J33, J43, J59, B49; ABC Private Credit Deal A Model v24, MODEL OUTPUT!F20:I20, F21; Diligence &amp; Structure Update p.11 · Basis: Readings on the observed ranges are [I]; alternative parameters are assumed; Deal A values are A except the plan (P) and the company's closure estimates (M) · Assumption: A-01, A-07, A-F2</t>
+          <t>Source: Observed ranges of Part 03 and Part 04 with the fact rows and exhibits in each cell; Alpha - FY27 Clinic Closure Data, Summary!J33, J43, J59, B49; Alder Point Credit Deal A Model v24, MODEL OUTPUT!F20:I20, F21; Diligence &amp; Structure Update p.11 · Basis: Readings on the observed ranges are [I]; alternative parameters are assumed; Deal A values are A except the plan (P) and the company's closure estimates (M) · Assumption: A-01, A-07, A-F2</t>
         </is>
       </c>
     </row>
@@ -57369,14 +57369,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Our reading on each component of ABC Private Credit's Deal B thesis (MS1 to MS6), with the depth of the evidence and what would change it; January 2023 to August 2026</t>
+          <t>Our reading on each component of Alder Point Credit's Deal B thesis (MS1 to MS6), with the depth of the evidence and what would change it; January 2023 to August 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Alder Point Credit asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -57593,7 +57593,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Newest cohort 18.9% in its 2025 owned months (company 18%); older cohorts 7.6% and 8.6% on book rent (company 9% and 9%); first-year same-store sales −8.5% / −4.1% / −6.6% / −9.2% by cohort (company −13.3% to −6.2%); first owned year 0.55x / 0.76x / 0.71x of seller EBITDA against Operator 8 0.59–0.70x (DLB Datapack; DLB ABC Private Credit Diligence Responses p.2; Historical Acquisition Detail; Part 06 section B)</t>
+          <t>Newest cohort 18.9% in its 2025 owned months (company 18%); older cohorts 7.6% and 8.6% on book rent (company 9% and 9%); first-year same-store sales −8.5% / −4.1% / −6.6% / −9.2% by cohort (company −13.3% to −6.2%); first owned year 0.55x / 0.76x / 0.71x of seller EBITDA against Operator 8 0.59–0.70x (DLB Datapack; DLB Alder Point Credit Diligence Responses p.2; Historical Acquisition Detail; Part 06 section B)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -57625,7 +57625,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Median household income $63,374 against $47,928; three-attribute clinics 19.5% four-wall margin against 4.8% for those with none or one; density and acquisition returns not shown (ABC Private Credit Diligence Requests 8.21.26, attribution tabs; Part 06 section C). On public census data the 2025–26 clinics sit in markets with about twice the households within three miles and 8% higher household income than earlier clinics (93 of 103 clinics matched); the company's household figures are not on the same basis.</t>
+          <t>Median household income $63,374 against $47,928; three-attribute clinics 19.5% four-wall margin against 4.8% for those with none or one; density and acquisition returns not shown (Alder Point Credit Diligence Requests 8.21.26, attribution tabs; Part 06 section C). On public census data the 2025–26 clinics sit in markets with about twice the households within three miles and 8% higher household income than earlier clinics (93 of 103 clinics matched); the company's household figures are not on the same basis.</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -57721,7 +57721,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Four-wall −25.9% on the seller's same months (January–July 2026); visit count −11.5% a day in Q1, −16.1% in Q2, −17.3% a day in July; company windows −21.8% (August) and −15.6% (September) without weekly data; value $33–46m on wellness clinic multiples (DBW Datapack; DBW ABC Private Credit Diligence Responses; Part 06 section F)</t>
+          <t>Four-wall −25.9% on the seller's same months (January–July 2026); visit count −11.5% a day in Q1, −16.1% in Q2, −17.3% a day in July; company windows −21.8% (August) and −15.6% (September) without weekly data; value $33–46m on wellness clinic multiples (DBW Datapack; DBW Alder Point Credit Diligence Responses; Part 06 section F)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -57731,7 +57731,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Four-wall EBITDA of $5.42m in January–July 2026, 25.9% below the seller's same months; visit count −11.9% in the first quarter (−11.5% a day), −16.1% in the second and −17.3% a day in July; the company's recovery to −15.6% in September rests on weekly data not in the files; a value of $33–46m reaches ABC Private Credit's $44m only at its top (Part 06 section F)</t>
+          <t>Four-wall EBITDA of $5.42m in January–July 2026, 25.9% below the seller's same months; visit count −11.9% in the first quarter (−11.5% a day), −16.1% in the second and −17.3% a day in July; the company's recovery to −15.6% in September rests on weekly data not in the files; a value of $33–46m reaches Alder Point Credit's $44m only at its top (Part 06 section F)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -57775,7 +57775,7 @@
     <row r="32" ht="65" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Source: Sections B to G of this part, with the documents and rows cited there: Project Bravo DLB Datapack (DLB-003), Historical Acquisition Detail (DLB-029), QoE Workbook LTM Mar-26 (DLB-022), Financing Model Jul-26 RF (DLB-008), ABC Private Credit Diligence Requests 8.21.26 (DLB-028), DBW Datapack (DLB-002), DLB ABC Private Credit Diligence Responses (DLB-033), DBW ABC Private Credit Diligence Responses (DLB-034); public census data around 110 matched clinics [I, C-PUB-5]. The financing component is read in Part 08 section C · Basis: Reading labels as in Exhibit 1.05 and Exhibit 8.02. Figures are actual (A) unless marked; seller closing EBITDA and cash-rent margins are pro forma (PF); the borrower's plan is projected (P)</t>
+          <t>Source: Sections B to G of this part, with the documents and rows cited there: Project Bravo DLB Datapack (DLB-003), Historical Acquisition Detail (DLB-029), QoE Workbook LTM Mar-26 (DLB-022), Financing Model Jul-26 RF (DLB-008), Alder Point Credit Diligence Requests 8.21.26 (DLB-028), DBW Datapack (DLB-002), DLB Alder Point Credit Diligence Responses (DLB-033), DBW Alder Point Credit Diligence Responses (DLB-034); public census data around 110 matched clinics [I, C-PUB-5]. The financing component is read in Part 08 section C · Basis: Reading labels as in Exhibit 1.05 and Exhibit 8.02. Figures are actual (A) unless marked; seller closing EBITDA and cash-rent margins are pro forma (PF); the borrower's plan is projected (P)</t>
         </is>
       </c>
     </row>
@@ -58091,7 +58091,7 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Reporting and cash figures stated in the DLB ABC Private Credit Diligence Responses (1 October 2026) against the data files supplied; company figure, data figure and how far they tie</t>
+          <t>Reporting and cash figures stated in the DLB Alder Point Credit Diligence Responses (1 October 2026) against the data files supplied; company figure, data figure and how far they tie</t>
         </is>
       </c>
     </row>
@@ -58252,7 +58252,7 @@
     <row r="58" ht="39" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>Source: DLB ABC Private Credit Diligence Responses (DLB-033) pp.8–9; ABC Private Credit Diligence Requests 8.21.26 (DLB-028) tab 5; Financing Model (Jul-26 RF) (DLB-008) BS!C53; QoE Workbook LTM Mar-26 (DLB-022); Project Bravo DLB Datapack (DLB-003) · Basis: Company figures [M]; data figures as read [F] or computed [I]; actual (A)</t>
+          <t>Source: DLB Alder Point Credit Diligence Responses (DLB-033) pp.8–9; Alder Point Credit Diligence Requests 8.21.26 (DLB-028) tab 5; Financing Model (Jul-26 RF) (DLB-008) BS!C53; QoE Workbook LTM Mar-26 (DLB-022); Project Bravo DLB Datapack (DLB-003) · Basis: Company figures [M]; data figures as read [F] or computed [I]; actual (A)</t>
         </is>
       </c>
     </row>
@@ -58493,7 +58493,7 @@
     <row r="68" ht="52" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>Source: Financing Model Jul-26 RF (DLB-008), consolidated income statement less the DBW segment and DBW corporate overhead tabs; QoE Workbook, 'DD #1 - Acquisition Expenses' (DLB-022); ABC Private Credit Diligence Requests, tab 6 (DLB-028); rows as shown; peers note C-26 · Basis: Now: A (LTM Mar-26) and PF (FY25 revenue); FY28E: P (borrower plan, including acquisitions not yet made); integration budget [M]; observed integration cost [I] on the like-for-like sub-lines named. DBW is read in Part 06 section F</t>
+          <t>Source: Financing Model Jul-26 RF (DLB-008), consolidated income statement less the DBW segment and DBW corporate overhead tabs; QoE Workbook, 'DD #1 - Acquisition Expenses' (DLB-022); Alder Point Credit Diligence Requests, tab 6 (DLB-028); rows as shown; peers note C-26 · Basis: Now: A (LTM Mar-26) and PF (FY25 revenue); FY28E: P (borrower plan, including acquisitions not yet made); integration budget [M]; observed integration cost [I] on the like-for-like sub-lines named. DBW is read in Part 06 section F</t>
         </is>
       </c>
     </row>
@@ -58507,7 +58507,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Figures stated in the DBW ABC Private Credit Diligence Responses (30 September 2026) against the DBW datapack and quality-of-earnings files; company figure, data figure and how far they tie</t>
+          <t>Figures stated in the DBW Alder Point Credit Diligence Responses (30 September 2026) against the DBW datapack and quality-of-earnings files; company figure, data figure and how far they tie</t>
         </is>
       </c>
     </row>
@@ -58690,7 +58690,7 @@
     <row r="80" ht="39" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>Source: DBW ABC Private Credit Diligence Responses (DLB-034) pp.1–4; DBW Datapack (Jul-26 RF) (DLB-002); DBW QoE workbook, 'DBW PF Adj. &amp; Walk' rows 11–49; Financing Model (Jul-26 RF) (DLB-008); Lender Update, 10 September 2026, p.3; Early Read p.6 · Basis: Company figures [M]; data figures as read [F] or computed [I]; the 2025 months are seller-system data</t>
+          <t>Source: DBW Alder Point Credit Diligence Responses (DLB-034) pp.1–4; DBW Datapack (Jul-26 RF) (DLB-002); DBW QoE workbook, 'DBW PF Adj. &amp; Walk' rows 11–49; Financing Model (Jul-26 RF) (DLB-008); Lender Update, 10 September 2026, p.3; Early Read p.6 · Basis: Company figures [M]; data figures as read [F] or computed [I]; the 2025 months are seller-system data</t>
         </is>
       </c>
     </row>
@@ -58973,17 +58973,17 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Post-audit pro forma $13.79m (DLB-5599); ABC Private Credit cash 0.34 of it (DLB-6302)</t>
+          <t>Post-audit pro forma $13.79m (DLB-5599); Alder Point Credit cash 0.34 of it (DLB-6302)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>$11.7m at the peer median; $5.7m at ABC Private Credit's own ratio</t>
+          <t>$11.7m at the peer median; $5.7m at Alder Point Credit's own ratio</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit cash-adjusted $5.7m only</t>
+          <t>Alder Point Credit cash-adjusted $5.7m only</t>
         </is>
       </c>
     </row>
@@ -59079,7 +59079,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>$5.9–6.3m × 5.3x = $37–38m; ABC Private Credit "$44m"</t>
+          <t>$5.9–6.3m × 5.3x = $37–38m; Alder Point Credit "$44m"</t>
         </is>
       </c>
     </row>
@@ -59133,12 +59133,12 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit E5 $11.16m</t>
+          <t>Alder Point Credit E5 $11.16m</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Up to 1.3x ABC Private Credit E5 if the "Action Needed" category closed with its full tail</t>
+          <t>Up to 1.3x Alder Point Credit E5 if the "Action Needed" category closed with its full tail</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -59329,14 +59329,14 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Our reading on each component of ABC Private Credit's Deal C thesis (ST1 to ST4), with the depth of the evidence and what would change it; FY2025 to July 2026</t>
+          <t>Our reading on each component of Alder Point Credit's Deal C thesis (ST1 to ST4), with the depth of the evidence and what would change it; FY2025 to July 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Alder Point Credit asked</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -59407,12 +59407,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Insufficient evidence (underwriting EBITDA, E5; Accounting Firm 1 QoE absent) — cash earnings contradicted while the affiliate bonuses continue. $9.2m of ABC Private Credit's $29.4m is pre-acquisition and letter-of-intent earnings; cash EBITDA after recurring deal costs was 0.31 of pro forma in FY2025, and about 0.59 if the bonuses end (Part 07 section D).</t>
+          <t>Insufficient evidence (underwriting EBITDA, E5; Accounting Firm 1 QoE absent) — cash earnings contradicted while the affiliate bonuses continue. $9.2m of Alder Point Credit's $29.4m is pre-acquisition and letter-of-intent earnings; cash EBITDA after recurring deal costs was 0.31 of pro forma in FY2025, and about 0.59 if the bonuses end (Part 07 section D).</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>FY2025 audit (actual); ABC Private Credit's Internal Diligence Exhibits (pro forma and projected); the cash share at the roll-up peers; no quality-of-earnings report.</t>
+          <t>FY2025 audit (actual); Alder Point Credit's Internal Diligence Exhibits (pro forma and projected); the cash share at the roll-up peers; no quality-of-earnings report.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -59453,14 +59453,14 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 7.02 — FY2024 to LTM Sep-26E: Deal C's audited clinic margin holds; its 2026 trend, the claimed acquired-clinic uplift and its cash earnings are where the evidence falls short of ABC Private Credit's initial view</t>
+          <t>Exhibit 7.02 — FY2024 to LTM Sep-26E: Deal C's audited clinic margin holds; its 2026 trend, the claimed acquired-clinic uplift and its cash earnings are where the evidence falls short of Alder Point Credit's initial view</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Our reading of each component of ABC Private Credit's Deal C thesis on the evidence supplied to date, with its basis, what holds, what does not and what would change it; FY2024 to LTM Sep-26E</t>
+          <t>Our reading of each component of Alder Point Credit's Deal C thesis on the evidence supplied to date, with its basis, what holds, what does not and what would change it; FY2024 to LTM Sep-26E</t>
         </is>
       </c>
     </row>
@@ -60217,7 +60217,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit asked</t>
+          <t>Alder Point Credit asked</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -60266,12 +60266,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Contradicted — on trailing leverage, cover and funding. On ABC Private Credit's $11.16m of EBITDA for the twelve months to July 2026 the $55m term loan reads 4.08x first lien, inside the 2.25–5.10x of the four 2025–26 first-lien prints on the same measure, and 7.59x with the HoldCo note, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on that EBITDA and 0.93x on the borrower's $14.77m; the pricing is high (S+5.55%, equal to the widest spread in the 2025–26 set), and the near-term acquisition batch is $8.8–11.8m short of committed sources (Part 08 section C).</t>
+          <t>Contradicted — on trailing leverage, cover and funding. On Alder Point Credit's $11.16m of EBITDA for the twelve months to July 2026 the $55m term loan reads 4.08x first lien, inside the 2.25–5.10x of the four 2025–26 first-lien prints on the same measure, and 7.59x with the HoldCo note, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on that EBITDA and 0.93x on the borrower's $14.77m; the pricing is high (S+5.55%, equal to the widest spread in the 2025–26 set), and the near-term acquisition batch is $8.8–11.8m short of committed sources (Part 08 section C).</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's response to the borrower's financing grid (19 September 2026) and the borrower's and ABC Private Credit's financing models (projected); post-audit earnings to July 2026 (pro forma); peer leverage prints from six core operators and cover prints from three, on mixed definitions.</t>
+          <t>Alder Point Credit's response to the borrower's financing grid (19 September 2026) and the borrower's and Alder Point Credit's financing models (projected); post-audit earnings to July 2026 (pro forma); peer leverage prints from six core operators and cover prints from three, on mixed definitions.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -60288,12 +60288,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Contradicted. The $204.3m first lien is 5.96x gross on ABC Private Credit's $29.4m, against 3.81–5.10x for the Operator 6, Operator 3 and Operator 4 prints of 2025–26 on the same earnings measure (Operator 7 2.25x proposal sits below); fixed-charge cover computes at 0.77x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m; $23.2m as printed), and at the 4.3x median the debt refinances only with at least 1.57% a year of EBITDA growth, against same-store clinic EBITDA of +1.0% for 2025 and −5.8% for the twelve months to July 2026 (Part 08 section D).</t>
+          <t>Contradicted. The $204.3m first lien is 5.96x gross on Alder Point Credit's $29.4m, against 3.81–5.10x for the Operator 6, Operator 3 and Operator 4 prints of 2025–26 on the same earnings measure (Operator 7 2.25x proposal sits below); fixed-charge cover computes at 0.77x on Alder Point Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m; $23.2m as printed), and at the 4.3x median the debt refinances only with at least 1.57% a year of EBITDA growth, against same-store clinic EBITDA of +1.0% for 2025 and −5.8% for the twelve months to July 2026 (Part 08 section D).</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's Early Read Memo v19 and Internal Diligence Exhibits (projected, including forecast and pre-acquisition months); the FY2025 audit (actual); first-lien prints from six operators, 2014 to 2026; a six-year refinancing calculation on stated anchors.</t>
+          <t>Alder Point Credit's Early Read Memo v19 and Internal Diligence Exhibits (projected, including forecast and pre-acquisition months); the FY2025 audit (actual); first-lien prints from six operators, 2014 to 2026; a six-year refinancing calculation on stated anchors.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -60310,7 +60310,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Insufficient evidence — sponsor-instrument terms missing. The $176.0m first lien is 5.30x gross on ABC Private Credit's $29.4m, above the 3.81–5.10x of the Operator 6, Operator 3 and Operator 4 prints; on a path with no acquisitions the senior loan refinances at the 4.3x median on flat earnings; a 17% cash coupon on the $21m sponsor instrument turns that into a $2.3m gap, and the $70m delayed-draw loan drawn at the audited deal-cost rate leaves total debt, including the sponsor instrument, $8.0m short (Part 08 section D).</t>
+          <t>Insufficient evidence — sponsor-instrument terms missing. The $176.0m first lien is 5.30x gross on Alder Point Credit's $29.4m, above the 3.81–5.10x of the Operator 6, Operator 3 and Operator 4 prints; on a path with no acquisitions the senior loan refinances at the 4.3x median on flat earnings; a 17% cash coupon on the $21m sponsor instrument turns that into a $2.3m gap, and the $70m delayed-draw loan drawn at the audited deal-cost rate leaves total debt, including the sponsor instrument, $8.0m short (Part 08 section D).</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -60405,7 +60405,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Supplier finance is repaid at close; first-lien leverage of 3.93x sits below Operator 6, Operator 3 and Operator 4 on the same rung; the leverage covenant is never within 1.0x of 7.50x; liquidity clears the $21m minimum by $12.4m in the lead case; ABC Private Credit's Diligence &amp; Structure Update states that the sale process has been launched</t>
+          <t>Supplier finance is repaid at close; first-lien leverage of 3.93x sits below Operator 6, Operator 3 and Operator 4 on the same rung; the leverage covenant is never within 1.0x of 7.50x; liquidity clears the $21m minimum by $12.4m in the lead case; Alder Point Credit's Diligence &amp; Structure Update states that the sale process has been launched</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -60437,17 +60437,17 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's $11.16m (term loan $55m); fixed-charge cover 0.61x on ABC Private Credit's $11.16m and 0.93x on the borrower's $14.77m (peer cover prints are on other definitions and are not set against these); S+5.55% equal to the widest spread in the set; batch short $8.8–11.8m (Part 08 section C)</t>
+          <t>4.08x first lien and 7.59x with the HoldCo note on Alder Point Credit's $11.16m (term loan $55m); fixed-charge cover 0.61x on Alder Point Credit's $11.16m and 0.93x on the borrower's $14.77m (peer cover prints are on other definitions and are not set against these); S+5.55% equal to the widest spread in the set; batch short $8.8–11.8m (Part 08 section C)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>First-lien leverage on the term loan alone is inside the 2.25–5.10x of the 2025–26 same-rung prints on every underwriting denominator (4.08x on ABC Private Credit's $11.16m) and reads 2.9–3.3x on the borrower's forward or pro forma bases; the pricing is high, S+5.55%, equal to the widest spread in the 2025–26 set, with 1.8–2.2% warrants</t>
+          <t>First-lien leverage on the term loan alone is inside the 2.25–5.10x of the 2025–26 same-rung prints on every underwriting denominator (4.08x on Alder Point Credit's $11.16m) and reads 2.9–3.3x on the borrower's forward or pro forma bases; the pricing is high, S+5.55%, equal to the widest spread in the 2025–26 set, with 1.8–2.2% warrants</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>With the $36.9m HoldCo note the stack reads 7.59x, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on ABC Private Credit's $11.16m and 0.93x on the borrower's $14.77m; the warrants are worth about $0.4–2.1m against $93.4m of commitments; the near-term batch is $8.8–11.8m short of committed sources</t>
+          <t>With the $36.9m HoldCo note the stack reads 7.59x, above every peer print that includes holding-company or sponsor notes (5.4–7.2x); fixed-charge cover computes at 0.61x on Alder Point Credit's $11.16m and 0.93x on the borrower's $14.77m; the warrants are worth about $0.4–2.1m against $93.4m of commitments; the near-term batch is $8.8–11.8m short of committed sources</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -60474,17 +60474,17 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>5.96x gross first lien on ABC Private Credit's underwriting EBITDA against 3.81–5.10x; fixed-charge cover computes at 0.77x on ABC Private Credit's cash EBITDA (0.22x on cash EBITDA after recurring deal costs); refinances at the 4.3x median only with at least 1.57% a year of EBITDA growth, against +1.0% and −5.8% observed (Part 08 section D)</t>
+          <t>5.96x gross first lien on Alder Point Credit's underwriting EBITDA against 3.81–5.10x; fixed-charge cover computes at 0.77x on Alder Point Credit's cash EBITDA (0.22x on cash EBITDA after recurring deal costs); refinances at the 4.3x median only with at least 1.57% a year of EBITDA growth, against +1.0% and −5.8% observed (Part 08 section D)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Cover computes at 0.96x on ABC Private Credit's $29.4m and 1.08x on the sponsor's $32.3m; with at least 1.57% a year of EBITDA growth on $29.4m Option Two refinances at the 4.3x median</t>
+          <t>Cover computes at 0.96x on Alder Point Credit's $29.4m and 1.08x on the sponsor's $32.3m; with at least 1.57% a year of EBITDA growth on $29.4m Option Two refinances at the 4.3x median</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>The 5.96x gross first lien is above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7); cover is 0.77x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m), against cash breakeven EBITDA of $26.0m; same-store clinic EBITDA grew +1.0% in 2025 and −5.8% for LTM July 2026, below the growth the refinancing needs</t>
+          <t>The 5.96x gross first lien is above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7); cover is 0.77x on Alder Point Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m), against cash breakeven EBITDA of $26.0m; same-store clinic EBITDA grew +1.0% in 2025 and −5.8% for LTM July 2026, below the growth the refinancing needs</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -60516,7 +60516,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Cover computes at 1.00x on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m) and 1.23x on $29.4m (term loan only, at S+451); on a no-acquisition path the senior tranche refinances at the 4.3x median on flat $29.4m</t>
+          <t>Cover computes at 1.00x on Alder Point Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m) and 1.23x on $29.4m (term loan only, at S+451); on a no-acquisition path the senior tranche refinances at the 4.3x median on flat $29.4m</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -60540,14 +60540,14 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 8.06 — The recapitalisation model of 29 September keeps $336m of commitments but replaces the delayed-draw loan with a $218m term loan and repays $145m of supplier finance at close: funded debt is $254m, 3.51x gross on the model's LTM 2Q27F EBITDA, against $152m and 1.9x in ABC Private Credit's model of September</t>
+          <t>Exhibit 8.06 — The recapitalisation model of 29 September keeps $336m of commitments but replaces the delayed-draw loan with a $218m term loan and repays $145m of supplier finance at close: funded debt is $254m, 3.51x gross on the model's LTM 2Q27F EBITDA, against $152m and 1.9x in Alder Point Credit's model of September</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Main terms of the LW draft term sheet of 21 September 2026 (with ABC Private Credit's Deal A model v24) against the recapitalisation model v06 of 29 September 2026, scenario 3</t>
+          <t>Main terms of the LW draft term sheet of 21 September 2026 (with Alder Point Credit's Deal A model v24) against the recapitalisation model v06 of 29 September 2026, scenario 3</t>
         </is>
       </c>
     </row>
@@ -60593,7 +60593,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Revolver $44m deemed drawn; term loan $111m; ABC Private Credit's model v24: $152m of bank debt</t>
+          <t>Revolver $44m deemed drawn; term loan $111m; Alder Point Credit's model v24: $152m of bank debt</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -60661,7 +60661,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>1.9x first lien on ABC Private Credit's $71.7m (LTM Sep-26, including a forecast quarter)</t>
+          <t>1.9x first lien on Alder Point Credit's $71.7m (LTM Sep-26, including a forecast quarter)</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -60729,7 +60729,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's model v24: $12m benefit from April 2027; $4.3m of closure cash and $4.3m of fees</t>
+          <t>Alder Point Credit's model v24: $12m benefit from April 2027; $4.3m of closure cash and $4.3m of fees</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -60775,14 +60775,14 @@
     <row r="45" ht="52" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Source: LW draft term sheet, 21 September 2026 (DLA-023); ABC Private Credit Deal A Model v24 (DLA-024); Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026): Scenario Drivers!E9, E13, E15, G23, G31, G36, G62:G92, G77; Sources &amp; Uses rows 10–20, I19; PF Cap Structure!E11, E13, O15, P15, P18, U8; Covenants!C65, C67, C144; Draw Schedule Summary!J39, row 101 · Basis: Terms as each document states them [F]; leverage on projected EBITDA (P). No term sheet later than 21 September 2026 is in the files, so the right-hand column gives the model's terms</t>
+          <t>Source: LW draft term sheet, 21 September 2026 (DLA-023); Alder Point Credit Deal A Model v24 (DLA-024); Project Alpha Recapitalization Model 1755.46.29 v06 (DLA-026): Scenario Drivers!E9, E13, E15, G23, G31, G36, G62:G92, G77; Sources &amp; Uses rows 10–20, I19; PF Cap Structure!E11, E13, O15, P15, P18, U8; Covenants!C65, C67, C144; Draw Schedule Summary!J39, row 101 · Basis: Terms as each document states them [F]; leverage on projected EBITDA (P). No term sheet later than 21 September 2026 is in the files, so the right-hand column gives the model's terms</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 8.10 — At close the $55m term loan reads 4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's LTM July 2026 EBITDA: first lien inside the 2.25–5.10x of the 2025–26 same-rung prints, the stack above every peer LV4 print</t>
+          <t>Exhibit 8.10 — At close the $55m term loan reads 4.08x first lien and 7.59x with the HoldCo note on Alder Point Credit's LTM July 2026 EBITDA: first lien inside the 2.25–5.10x of the 2025–26 same-rung prints, the stack above every peer LV4 print</t>
         </is>
       </c>
     </row>
@@ -60862,7 +60862,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>E5 ABC Private Credit LTM Jul-26 $11.16m (PF; DLB-9352 / 7904)</t>
+          <t>E5 Alder Point Credit LTM Jul-26 $11.16m (PF; DLB-9352 / 7904)</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -60950,14 +60950,14 @@
     <row r="56" ht="39" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>Source: DLB-026 (ABC Private Credit response to the Proposed Financing Grid); DLB-008 (Financing Model, Jul-26 RF); DLB-9234..9583; peer rows as listed · Basis: P (structure at close); each denominator's basis (A, PF, P) as marked in its row · Assumption: LV1 = term loan; LV3 adds the seller note $5.6m, other debt $0.8m and equipment leases $2.2m; LV4 adds the HoldCo note at $36.9m. Gross of cash. LV6 cannot be computed: no debt-like balances are disclosed (DLB-9584)</t>
+          <t>Source: DLB-026 (Alder Point Credit response to the Proposed Financing Grid); DLB-008 (Financing Model, Jul-26 RF); DLB-9234..9583; peer rows as listed · Basis: P (structure at close); each denominator's basis (A, PF, P) as marked in its row · Assumption: LV1 = term loan; LV3 adds the seller note $5.6m, other debt $0.8m and equipment leases $2.2m; LV4 adds the HoldCo note at $36.9m. Gross of cash. LV6 cannot be computed: no debt-like balances are disclosed (DLB-9584)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Exhibit 8.14 — Option Two's 5.96x and Option One's 5.30x gross first lien on ABC Private Credit's $29.4m sit above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7) and above the 4.3x closed median since 2014</t>
+          <t>Exhibit 8.14 — Option Two's 5.96x and Option One's 5.30x gross first lien on Alder Point Credit's $29.4m sit above every 2025–26 print on the same rung (3.81–5.10x at Operator 6, Operator 3 and Operator 4; 2.25x at Operator 7) and above the 4.3x closed median since 2014</t>
         </is>
       </c>
     </row>
@@ -61511,7 +61511,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Financing sensitivities of the Deal B and Deal C proposals: ABC Private Credit's case, what the evidence shows, the value tested and its effect; leverage and cover x, amounts $m; terms of September 2026, maturities December 2030 and September 2032</t>
+          <t>Financing sensitivities of the Deal B and Deal C proposals: Alder Point Credit's case, what the evidence shows, the value tested and its effect; leverage and cover x, amounts $m; terms of September 2026, maturities December 2030 and September 2032</t>
         </is>
       </c>
     </row>
@@ -61528,7 +61528,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>ABC Private Credit's case</t>
+          <t>Alder Point Credit's case</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -61560,7 +61560,7 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>$55m term loan at 4.08x first lien and 7.59x with the HoldCo note on ABC Private Credit's $11.16m, LTM July 2026 (DLB-9352; DLB-9355)</t>
+          <t>$55m term loan at 4.08x first lien and 7.59x with the HoldCo note on Alder Point Credit's $11.16m, LTM July 2026 (DLB-9352; DLB-9355)</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -61575,7 +61575,7 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>First lien reads inside the 2025–26 same-rung set on underwriting EBITDA and above it on post-audit adjusted EBITDA (E2, $8.51m); the stack is above every peer LV4 print on ABC Private Credit's EBITDA (Part 08 section C)</t>
+          <t>First lien reads inside the 2025–26 same-rung set on underwriting EBITDA and above it on post-audit adjusted EBITDA (E2, $8.51m); the stack is above every peer LV4 print on Alder Point Credit's EBITDA (Part 08 section C)</t>
         </is>
       </c>
     </row>
@@ -61592,7 +61592,7 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>FCCR_CD on ABC Private Credit's $11.16m with next-twelve-month charges of $9.38m (DLB-9610)</t>
+          <t>FCCR_CD on Alder Point Credit's $11.16m with next-twelve-month charges of $9.38m (DLB-9610)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -61602,12 +61602,12 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit pro forma), 0.61x (ABC Private Credit's $11.16m), 0.34x (post-audit $8.51m) (DLB-9603..9607)</t>
+          <t>1.08x ($16.1m), 0.93x ($14.77m), 1.00x (post-audit pro forma), 0.61x (Alder Point Credit's $11.16m), 0.34x (post-audit $8.51m) (DLB-9603..9607)</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Cover is about 1x on the borrower's EBITDA and below 1x on ABC Private Credit's; the peer prints are on different definitions, so no position is taken</t>
+          <t>Cover is about 1x on the borrower's EBITDA and below 1x on Alder Point Credit's; the peer prints are on different definitions, so no position is taken</t>
         </is>
       </c>
     </row>
@@ -61634,12 +61634,12 @@
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Total leverage 7.85–8.25x on ABC Private Credit's $11.16m and 6.00–6.35x on $14.77m</t>
+          <t>Total leverage 7.85–8.25x on Alder Point Credit's $11.16m and 6.00–6.35x on $14.77m</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>With EBITDA flat, total leverage on ABC Private Credit's EBITDA moves further above every peer LV4 print within a year; on $14.77m it stays inside the 5.4–7.2x range</t>
+          <t>With EBITDA flat, total leverage on Alder Point Credit's EBITDA moves further above every peer LV4 print within a year; on $14.77m it stays inside the 5.4–7.2x range</t>
         </is>
       </c>
     </row>
@@ -61671,7 +61671,7 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Both thresholds sit above today's $11.16m on ABC Private Credit's measure and $13.79m post-audit</t>
+          <t>Both thresholds sit above today's $11.16m on Alder Point Credit's measure and $13.79m post-audit</t>
         </is>
       </c>
     </row>
@@ -61688,7 +61688,7 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>$26m DDTL and $11.1m revolver; cash at close $5.03m (ABC Private Credit model) or $2.46m (borrower model) (DLB-026; DLB-6351; DLB-5662)</t>
+          <t>$26m DDTL and $11.1m revolver; cash at close $5.03m (Alder Point Credit model) or $2.46m (borrower model) (DLB-026; DLB-6351; DLB-5662)</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -61720,7 +61720,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Option Two's $204.3m first lien at 5.96x gross on ABC Private Credit's $29.4m, LTM September 2026E, including $9.2m of pre-acquisition and LOI earnings (DLC-4725; DLC-4183)</t>
+          <t>Option Two's $204.3m first lien at 5.96x gross on Alder Point Credit's $29.4m, LTM September 2026E, including $9.2m of pre-acquisition and LOI earnings (DLC-4725; DLC-4183)</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -61730,7 +61730,7 @@
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>5.19x net on the sponsor's $32.3m; 7.24x gross on ABC Private Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); 20.0x gross on $8.6m of cash EBITDA after recurring deal costs (DLC-4712; DLC-4739; DLC-4781)</t>
+          <t>5.19x net on the sponsor's $32.3m; 7.24x gross on Alder Point Credit's cash EBITDA with the $1.0m non-cash impairment added back ($24.9m); 20.0x gross on $8.6m of cash EBITDA after recurring deal costs (DLC-4712; DLC-4739; DLC-4781)</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -61752,7 +61752,7 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>ABC Private Credit's coverage method on its cash EBITDA</t>
+          <t>Alder Point Credit's coverage method on its cash EBITDA</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -61784,7 +61784,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Option Two on ABC Private Credit's $29.4m, no-acquisition path to September 2032 (note C-90)</t>
+          <t>Option Two on Alder Point Credit's $29.4m, no-acquisition path to September 2032 (note C-90)</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -61968,7 +61968,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Covenant levels well above the modelled path (4.53x peak on ABC Private Credit's model v24)</t>
+          <t>Covenant levels well above the modelled path (4.53x peak on Alder Point Credit's model v24)</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -62093,7 +62093,7 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Closure-cash add-backs capped at $21m to FY29 and $13m after, the first cohort fully added back "per ABC Private Credit verbal" (Covenants rows 112–99; Scenario Drivers rows 24–23)</t>
+          <t>Closure-cash add-backs capped at $21m to FY29 and $13m after, the first cohort fully added back "per Alder Point Credit verbal" (Covenants rows 112–99; Scenario Drivers rows 24–23)</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -62188,7 +62188,7 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Delayed-draw amortisation; debt carried in ABC Private Credit's model v24</t>
+          <t>Delayed-draw amortisation; debt carried in Alder Point Credit's model v24</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
